--- a/Pradiniai.xlsx
+++ b/Pradiniai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agentura2020.sharepoint.com/sites/VidurioLietuvosaplinkostyrimuskyrius/Bendrai naudojami dokumentai/EB7-014 Darbuotojų failai/Tomo/Python 3.14.3/Skaiciavimai/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_45EDA4434E0550A4F20679E990E356986B43F608" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0EE2247-77BE-4A5C-A8F7-E8975B5E3EA4}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_45EDA4434ED551BD12A477E990E356986B43F608" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3CE6ABA-12FC-4E33-8EE7-832101478D4A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -453,4 +453,317 @@
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="453e7e53-5eb2-45cf-b2ab-34c867e554b8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="aa0d983d-359a-438c-9953-3af1a8ac0831" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumentas" ma:contentTypeID="0x010100BAB57CF81AE55C4698AAD22D302297F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Kurkite naują dokumentą." ma:contentTypeScope="" ma:versionID="49ab401eb4052690d2a2629974c22fd6">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="453e7e53-5eb2-45cf-b2ab-34c867e554b8" xmlns:ns3="aa0d983d-359a-438c-9953-3af1a8ac0831" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab9969d50e0b13c63bc5bd0499c928dc" ns2:_="" ns3:_="">
+    <xsd:import namespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
+    <xsd:import namespace="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="15" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="16" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Vaizdų žymės" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="993cf2ba-b7a7-49f7-97d1-76e12a88c412" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="23" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="aa0d983d-359a-438c-9953-3af1a8ac0831" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{82c4fa3c-500e-4213-91e5-1b9e2014ea63}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="aa0d983d-359a-438c-9953-3af1a8ac0831">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="21" nillable="true" ma:displayName="Bendrinama su" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="22" nillable="true" ma:displayName="Bendrinta su išsamia informacija" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Turinio tipas"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Antraštė"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF4C073-65F7-41BE-937B-140FDF21FA3E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
+    <ds:schemaRef ds:uri="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20BE762B-AE2C-417A-819B-FA4287787AAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C8B0016-1DF9-4A25-A8C3-29385697207A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
+    <ds:schemaRef ds:uri="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Pradiniai.xlsx
+++ b/Pradiniai.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Pradiniai" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,8 +17,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.\1"/>
+    <numFmt numFmtId="165" formatCode="0.1"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +32,21 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <charset val="186"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <charset val="186"/>
+      <family val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="186"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
@@ -43,7 +62,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -73,6 +92,21 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -130,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -138,31 +172,54 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Įprastas" xfId="0" builtinId="0"/>
@@ -554,7 +611,7 @@
       </c>
     </row>
     <row r="6" ht="50" customHeight="1">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="B6" s="2" t="n">
@@ -590,121 +647,121 @@
   </cols>
   <sheetData>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Išmatuotas diferencinis slėgis taškuose 1 linija, Pdi, hPa</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Išmatuotas diferencinis slėgis taškuose 2 linija, Pdi, hPa</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>Išmatuotas diferencinis slėgis taškuose 3 linija, Pdi, hPa</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Išmatuotas diferencinis slėgis taškuose 4 linija, Pdi, hPa</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Išmatuotas diferencinis slėgis taškuose 5 linija, Pdi, hPa</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>Atmosferinis slėgis P, hPa</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="14" t="n">
         <v>1012</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="13" t="n">
         <v>-0.25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="12" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="13" t="n"/>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -721,9 +778,65 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="G5:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
-  <sheetData/>
+  <cols>
+    <col width="15" customWidth="1" min="7" max="8"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="5" ht="39" customHeight="1">
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Išmatuota O2 koncentracija (%)</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>Išmatuota CO2 koncentracija (%)</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>Temperatūra ortakyje tor (°C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="G6" s="17" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I6" s="19" t="n">
+        <v>40.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="G7" s="17" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <v>39.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="G8" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Pradiniai.xlsx
+++ b/Pradiniai.xlsx
@@ -17,12 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="0.\1"/>
-    <numFmt numFmtId="165" formatCode="0.1"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +30,6 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="186"/>
-      <family val="2"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
@@ -41,13 +37,6 @@
       <name val="Times New Roman"/>
       <charset val="186"/>
       <family val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="186"/>
-      <family val="2"/>
-      <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
@@ -62,27 +51,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -164,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -172,51 +146,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -611,7 +578,7 @@
       </c>
     </row>
     <row r="6" ht="50" customHeight="1">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="8" t="n">
         <v>46063</v>
       </c>
       <c r="B6" s="2" t="n">
@@ -647,121 +614,121 @@
   </cols>
   <sheetData>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Išmatuotas diferencinis slėgis taškuose 1 linija, Pdi, hPa</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Išmatuotas diferencinis slėgis taškuose 2 linija, Pdi, hPa</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>Išmatuotas diferencinis slėgis taškuose 3 linija, Pdi, hPa</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Išmatuotas diferencinis slėgis taškuose 4 linija, Pdi, hPa</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Išmatuotas diferencinis slėgis taškuose 5 linija, Pdi, hPa</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Atmosferinis slėgis P, hPa</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n">
+      <c r="A6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="13" t="n">
         <v>1012</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="12" t="n">
         <v>-0.25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n">
+      <c r="A8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
+      <c r="A9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="16" t="n"/>
-      <c r="G9" s="16" t="n"/>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -778,61 +745,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="G5:I8"/>
+  <dimension ref="A2:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="15" customWidth="1" min="7" max="8"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="1" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="5" ht="39" customHeight="1">
-      <c r="G5" s="12" t="inlineStr">
+    <row r="2" ht="43.5" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Išmatuota O2 koncentracija (%)</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Išmatuota CO2 koncentracija (%)</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>Temperatūra ortakyje tor (°C)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="G6" s="17" t="n">
+    <row r="3">
+      <c r="A3" s="16" t="n">
         <v>10.02</v>
       </c>
-      <c r="H6" s="17" t="n">
+      <c r="B3" s="16" t="n">
         <v>4.1</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="C3" s="17" t="n">
         <v>40.2</v>
       </c>
     </row>
-    <row r="7">
-      <c r="G7" s="17" t="n">
+    <row r="4">
+      <c r="A4" s="16" t="n">
         <v>9.98</v>
       </c>
-      <c r="H7" s="17" t="n">
+      <c r="B4" s="16" t="n">
         <v>3.9</v>
       </c>
-      <c r="I7" s="19" t="n">
+      <c r="C4" s="17" t="n">
         <v>39.8</v>
       </c>
     </row>
-    <row r="8">
-      <c r="G8" s="17" t="n">
+    <row r="5">
+      <c r="A5" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="H8" s="17" t="n">
+      <c r="B5" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="I8" s="19" t="n">
+      <c r="C5" s="17" t="n">
         <v>40</v>
       </c>
     </row>

--- a/Pradiniai.xlsx
+++ b/Pradiniai.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +40,11 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
@@ -51,7 +56,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -81,6 +86,21 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -138,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -146,44 +166,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -578,7 +604,7 @@
       </c>
     </row>
     <row r="6" ht="50" customHeight="1">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="B6" s="2" t="n">
@@ -614,121 +640,121 @@
   </cols>
   <sheetData>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Išmatuotas diferencinis slėgis taškuose 1 linija, Pdi, hPa</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Išmatuotas diferencinis slėgis taškuose 2 linija, Pdi, hPa</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Išmatuotas diferencinis slėgis taškuose 3 linija, Pdi, hPa</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Išmatuotas diferencinis slėgis taškuose 4 linija, Pdi, hPa</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Išmatuotas diferencinis slėgis taškuose 5 linija, Pdi, hPa</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Atmosferinis slėgis P, hPa</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="15" t="n">
         <v>1012</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="14" t="n">
         <v>-0.25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n">
+      <c r="A7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="16" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n">
+      <c r="A9" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -754,52 +780,52 @@
   </cols>
   <sheetData>
     <row r="2" ht="43.5" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Išmatuota O2 koncentracija (%)</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Išmatuota CO2 koncentracija (%)</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>Temperatūra ortakyje tor (°C)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="18" t="n">
         <v>10.02</v>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="18" t="n">
         <v>4.1</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="19" t="n">
         <v>40.2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="18" t="n">
         <v>9.98</v>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="18" t="n">
         <v>3.9</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="19" t="n">
         <v>39.8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="19" t="n">
         <v>40</v>
       </c>
     </row>

--- a/Pradiniai.xlsx
+++ b/Pradiniai.xlsx
@@ -1,82 +1,164 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agentura2020.sharepoint.com/sites/VidurioLietuvosaplinkostyrimuskyrius/Bendrai naudojami dokumentai/EB7-014 Darbuotojų failai/Tomo/Python 3.14.3/Skaiciavimai/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_4FB90F5749670F7B0C56330294F34895116CB898" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{475B4C15-3DAD-426E-9C00-5AE8625FB2B8}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Pradiniai" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Greitis" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Paėmimas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Pradiniai" sheetId="1" r:id="rId1"/>
+    <sheet name="Greitis" sheetId="2" r:id="rId2"/>
+    <sheet name="Paėmimas" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="27">
+  <si>
+    <t>Matavimo data</t>
+  </si>
+  <si>
+    <t>Ėminių registracijos Nr. T-107-2026-E-</t>
+  </si>
+  <si>
+    <t>Objekto pavadinimas, adresas, taršos šaltinio Nr.</t>
+  </si>
+  <si>
+    <t>Išmatuotas diferencinis slėgis taškuose 1 linija, Pdi, hPa</t>
+  </si>
+  <si>
+    <t>Išmatuotas diferencinis slėgis taškuose 2 linija, Pdi, hPa</t>
+  </si>
+  <si>
+    <t>Išmatuotas diferencinis slėgis taškuose 3 linija, Pdi, hPa</t>
+  </si>
+  <si>
+    <t>Išmatuotas diferencinis slėgis taškuose 4 linija, Pdi, hPa</t>
+  </si>
+  <si>
+    <t>Išmatuotas diferencinis slėgis taškuose 5 linija, Pdi, hPa</t>
+  </si>
+  <si>
+    <t>Atmosferinis slėgis P, hPa</t>
+  </si>
+  <si>
+    <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
+  </si>
+  <si>
+    <t>Išmatuota O2 koncentracija (%)</t>
+  </si>
+  <si>
+    <t>Išmatuota CO2 koncentracija (%)</t>
+  </si>
+  <si>
+    <t>Temperatūra ortakyje tor (°C)</t>
+  </si>
+  <si>
+    <t>1 filtras</t>
+  </si>
+  <si>
+    <t>1 linija</t>
+  </si>
+  <si>
+    <t>2 linija</t>
+  </si>
+  <si>
+    <t>3 linija</t>
+  </si>
+  <si>
+    <t>4 linija</t>
+  </si>
+  <si>
+    <t>5 linija</t>
+  </si>
+  <si>
+    <t>Slėgis prieš rotametrą ΔPr (±hPa)</t>
+  </si>
+  <si>
+    <t>Antgalio diametras da (mm)</t>
+  </si>
+  <si>
+    <t>Siurbimo laikas t (min)</t>
+  </si>
+  <si>
+    <t>Siurbimo greitis Vo (l/min)</t>
+  </si>
+  <si>
+    <t>Siurbiamų dujų temperatūra prieš rotametrą tr (°C)</t>
+  </si>
+  <si>
+    <t>2 filtras</t>
+  </si>
+  <si>
+    <t>3 filtras</t>
+  </si>
+  <si>
+    <t>Ekopartneris</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="186"/>
-      <family val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -118,174 +200,65 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Įprastas" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -573,47 +546,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A5:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Matavimo data</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Ėminių registracijos Nr. T-107-2026-E-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>Objekto pavadinimas, adresas, taršos šaltinio Nr.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="50" customHeight="1">
-      <c r="A6" s="3" t="n">
+    <row r="5" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="13">
         <v>46063</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="2">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Ekopartneris</t>
-        </is>
+      <c r="C6" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -622,139 +583,116 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A5:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="5"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="7"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col min="1" max="5" width="15" customWidth="1"/>
+    <col min="6" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Išmatuotas diferencinis slėgis taškuose 1 linija, Pdi, hPa</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Išmatuotas diferencinis slėgis taškuose 2 linija, Pdi, hPa</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Išmatuotas diferencinis slėgis taškuose 3 linija, Pdi, hPa</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Išmatuotas diferencinis slėgis taškuose 4 linija, Pdi, hPa</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>Išmatuotas diferencinis slėgis taškuose 5 linija, Pdi, hPa</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>Atmosferinis slėgis P, hPa</t>
-        </is>
-      </c>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="14" t="n">
+    <row r="5" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3">
         <v>2</v>
       </c>
-      <c r="C6" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="14" t="n">
+      <c r="C6" s="3">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3">
         <v>4</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="3">
         <v>5</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="7">
         <v>1012</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="10">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="14" t="n">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3">
         <v>2</v>
       </c>
-      <c r="C7" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="14" t="n">
+      <c r="C7" s="3">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3">
         <v>4</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="3">
         <v>5</v>
       </c>
-      <c r="F7" s="16" t="n"/>
-      <c r="G7" s="16" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="14" t="n">
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="3">
         <v>2</v>
       </c>
-      <c r="C8" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" s="14" t="n">
+      <c r="C8" s="3">
+        <v>3</v>
+      </c>
+      <c r="D8" s="3">
         <v>4</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="3">
         <v>5</v>
       </c>
-      <c r="F8" s="16" t="n"/>
-      <c r="G8" s="16" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="14" t="n">
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>1</v>
+      </c>
+      <c r="B9" s="3">
         <v>2</v>
       </c>
-      <c r="C9" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="14" t="n">
+      <c r="C9" s="3">
+        <v>3</v>
+      </c>
+      <c r="D9" s="3">
         <v>4</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="3">
         <v>5</v>
       </c>
-      <c r="F9" s="17" t="n"/>
-      <c r="G9" s="17" t="n"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -766,70 +704,1468 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A2:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A2:AC31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="2"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col min="1" max="30" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="43.5" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>Išmatuota O2 koncentracija (%)</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>Išmatuota CO2 koncentracija (%)</t>
-        </is>
-      </c>
-      <c r="C2" s="13" t="inlineStr">
-        <is>
-          <t>Temperatūra ortakyje tor (°C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="18" t="n">
+    <row r="2" spans="1:29" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A3" s="14">
         <v>10.02</v>
       </c>
-      <c r="B3" s="18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="C3" s="19" t="n">
-        <v>40.2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="B3" s="14">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C3" s="15">
+        <v>40.200000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A4" s="14">
         <v>9.98</v>
       </c>
-      <c r="B4" s="18" t="n">
+      <c r="B4" s="14">
         <v>3.9</v>
       </c>
-      <c r="C4" s="19" t="n">
-        <v>39.8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="C4" s="15">
+        <v>39.799999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A5" s="14">
         <v>10</v>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="14">
         <v>4</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="15">
         <v>40</v>
       </c>
     </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="G8" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="M8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="S8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="12"/>
+      <c r="Y8" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z8" s="12"/>
+      <c r="AA8" s="12"/>
+      <c r="AB8" s="12"/>
+      <c r="AC8" s="12"/>
+    </row>
+    <row r="9" spans="1:29" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC9" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A10" s="5">
+        <v>111</v>
+      </c>
+      <c r="B10" s="5">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4">
+        <v>3</v>
+      </c>
+      <c r="D10" s="4">
+        <v>112</v>
+      </c>
+      <c r="E10" s="5">
+        <v>113</v>
+      </c>
+      <c r="G10" s="5">
+        <v>121</v>
+      </c>
+      <c r="H10" s="5">
+        <f t="shared" ref="H10:I13" si="0">B10</f>
+        <v>1</v>
+      </c>
+      <c r="I10" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J10" s="4">
+        <v>122</v>
+      </c>
+      <c r="K10" s="5">
+        <v>123</v>
+      </c>
+      <c r="M10" s="5">
+        <v>131</v>
+      </c>
+      <c r="N10" s="5">
+        <f t="shared" ref="N10:O13" si="1">B10</f>
+        <v>1</v>
+      </c>
+      <c r="O10" s="4">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="P10" s="4">
+        <v>132</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>133</v>
+      </c>
+      <c r="S10" s="5">
+        <v>141</v>
+      </c>
+      <c r="T10" s="5">
+        <f t="shared" ref="T10:U13" si="2">B10</f>
+        <v>1</v>
+      </c>
+      <c r="U10" s="4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="V10" s="4">
+        <v>142</v>
+      </c>
+      <c r="W10" s="5">
+        <v>143</v>
+      </c>
+      <c r="Y10" s="5">
+        <v>151</v>
+      </c>
+      <c r="Z10" s="5">
+        <f t="shared" ref="Z10:AA13" si="3">B10</f>
+        <v>1</v>
+      </c>
+      <c r="AA10" s="4">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="AB10" s="4">
+        <v>152</v>
+      </c>
+      <c r="AC10" s="5">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A11" s="5">
+        <v>111</v>
+      </c>
+      <c r="B11" s="5">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4">
+        <v>3</v>
+      </c>
+      <c r="D11" s="4">
+        <v>112</v>
+      </c>
+      <c r="E11" s="5">
+        <v>113</v>
+      </c>
+      <c r="G11" s="5">
+        <v>121</v>
+      </c>
+      <c r="H11" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I11" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J11" s="4">
+        <v>122</v>
+      </c>
+      <c r="K11" s="5">
+        <v>123</v>
+      </c>
+      <c r="M11" s="5">
+        <v>131</v>
+      </c>
+      <c r="N11" s="5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O11" s="4">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="P11" s="4">
+        <v>132</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>133</v>
+      </c>
+      <c r="S11" s="5">
+        <v>141</v>
+      </c>
+      <c r="T11" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="U11" s="4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="V11" s="4">
+        <v>142</v>
+      </c>
+      <c r="W11" s="5">
+        <v>143</v>
+      </c>
+      <c r="Y11" s="5">
+        <v>151</v>
+      </c>
+      <c r="Z11" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AA11" s="4">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="AB11" s="4">
+        <v>152</v>
+      </c>
+      <c r="AC11" s="5">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
+        <v>111</v>
+      </c>
+      <c r="B12" s="5">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4">
+        <v>3</v>
+      </c>
+      <c r="D12" s="4">
+        <v>112</v>
+      </c>
+      <c r="E12" s="5">
+        <v>113</v>
+      </c>
+      <c r="G12" s="5">
+        <v>121</v>
+      </c>
+      <c r="H12" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I12" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J12" s="4">
+        <v>122</v>
+      </c>
+      <c r="K12" s="5">
+        <v>123</v>
+      </c>
+      <c r="M12" s="5">
+        <v>131</v>
+      </c>
+      <c r="N12" s="5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O12" s="4">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="P12" s="4">
+        <v>132</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>133</v>
+      </c>
+      <c r="S12" s="5">
+        <v>141</v>
+      </c>
+      <c r="T12" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="U12" s="4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="V12" s="4">
+        <v>142</v>
+      </c>
+      <c r="W12" s="5">
+        <v>143</v>
+      </c>
+      <c r="Y12" s="5">
+        <v>151</v>
+      </c>
+      <c r="Z12" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AA12" s="4">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="AB12" s="4">
+        <v>152</v>
+      </c>
+      <c r="AC12" s="5">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A13" s="5">
+        <v>111</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4">
+        <v>3</v>
+      </c>
+      <c r="D13" s="4">
+        <v>112</v>
+      </c>
+      <c r="E13" s="5">
+        <v>113</v>
+      </c>
+      <c r="G13" s="5">
+        <v>121</v>
+      </c>
+      <c r="H13" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I13" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J13" s="4">
+        <v>122</v>
+      </c>
+      <c r="K13" s="5">
+        <v>123</v>
+      </c>
+      <c r="M13" s="5">
+        <v>131</v>
+      </c>
+      <c r="N13" s="5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O13" s="4">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="P13" s="4">
+        <v>132</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>133</v>
+      </c>
+      <c r="S13" s="5">
+        <v>141</v>
+      </c>
+      <c r="T13" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="U13" s="4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="V13" s="4">
+        <v>142</v>
+      </c>
+      <c r="W13" s="5">
+        <v>143</v>
+      </c>
+      <c r="Y13" s="5">
+        <v>151</v>
+      </c>
+      <c r="Z13" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AA13" s="4">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="AB13" s="4">
+        <v>152</v>
+      </c>
+      <c r="AC13" s="5">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A17" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="G17" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="M17" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
+      <c r="S17" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="T17" s="12"/>
+      <c r="U17" s="12"/>
+      <c r="V17" s="12"/>
+      <c r="W17" s="12"/>
+      <c r="Y17" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z17" s="12"/>
+      <c r="AA17" s="12"/>
+      <c r="AB17" s="12"/>
+      <c r="AC17" s="12"/>
+    </row>
+    <row r="18" spans="1:29" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC18" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A19" s="5">
+        <v>211</v>
+      </c>
+      <c r="B19" s="5">
+        <f t="shared" ref="B19:C22" si="4">B10</f>
+        <v>1</v>
+      </c>
+      <c r="C19" s="4">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="D19" s="4">
+        <v>212</v>
+      </c>
+      <c r="E19" s="5">
+        <v>213</v>
+      </c>
+      <c r="G19" s="5">
+        <v>221</v>
+      </c>
+      <c r="H19" s="5">
+        <f t="shared" ref="H19:I22" si="5">B10</f>
+        <v>1</v>
+      </c>
+      <c r="I19" s="4">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="J19" s="4">
+        <v>222</v>
+      </c>
+      <c r="K19" s="5">
+        <v>223</v>
+      </c>
+      <c r="M19" s="5">
+        <v>231</v>
+      </c>
+      <c r="N19" s="5">
+        <f t="shared" ref="N19:O22" si="6">B10</f>
+        <v>1</v>
+      </c>
+      <c r="O19" s="4">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="P19" s="4">
+        <v>232</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>233</v>
+      </c>
+      <c r="S19" s="5">
+        <v>241</v>
+      </c>
+      <c r="T19" s="5">
+        <f t="shared" ref="T19:U22" si="7">B10</f>
+        <v>1</v>
+      </c>
+      <c r="U19" s="4">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="V19" s="4">
+        <v>242</v>
+      </c>
+      <c r="W19" s="5">
+        <v>243</v>
+      </c>
+      <c r="Y19" s="5">
+        <v>251</v>
+      </c>
+      <c r="Z19" s="5">
+        <f t="shared" ref="Z19:AA22" si="8">B10</f>
+        <v>1</v>
+      </c>
+      <c r="AA19" s="4">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="AB19" s="4">
+        <v>252</v>
+      </c>
+      <c r="AC19" s="5">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A20" s="5">
+        <v>211</v>
+      </c>
+      <c r="B20" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="C20" s="4">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="D20" s="4">
+        <v>212</v>
+      </c>
+      <c r="E20" s="5">
+        <v>213</v>
+      </c>
+      <c r="G20" s="5">
+        <v>221</v>
+      </c>
+      <c r="H20" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I20" s="4">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="J20" s="4">
+        <v>222</v>
+      </c>
+      <c r="K20" s="5">
+        <v>223</v>
+      </c>
+      <c r="M20" s="5">
+        <v>231</v>
+      </c>
+      <c r="N20" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="O20" s="4">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="P20" s="4">
+        <v>232</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>233</v>
+      </c>
+      <c r="S20" s="5">
+        <v>241</v>
+      </c>
+      <c r="T20" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="U20" s="4">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="V20" s="4">
+        <v>242</v>
+      </c>
+      <c r="W20" s="5">
+        <v>243</v>
+      </c>
+      <c r="Y20" s="5">
+        <v>251</v>
+      </c>
+      <c r="Z20" s="5">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AA20" s="4">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="AB20" s="4">
+        <v>252</v>
+      </c>
+      <c r="AC20" s="5">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <v>211</v>
+      </c>
+      <c r="B21" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="C21" s="4">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="D21" s="4">
+        <v>212</v>
+      </c>
+      <c r="E21" s="5">
+        <v>213</v>
+      </c>
+      <c r="G21" s="5">
+        <v>221</v>
+      </c>
+      <c r="H21" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I21" s="4">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="J21" s="4">
+        <v>222</v>
+      </c>
+      <c r="K21" s="5">
+        <v>223</v>
+      </c>
+      <c r="M21" s="5">
+        <v>231</v>
+      </c>
+      <c r="N21" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="O21" s="4">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="P21" s="4">
+        <v>232</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>233</v>
+      </c>
+      <c r="S21" s="5">
+        <v>241</v>
+      </c>
+      <c r="T21" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="U21" s="4">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="V21" s="4">
+        <v>242</v>
+      </c>
+      <c r="W21" s="5">
+        <v>243</v>
+      </c>
+      <c r="Y21" s="5">
+        <v>251</v>
+      </c>
+      <c r="Z21" s="5">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AA21" s="4">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="AB21" s="4">
+        <v>252</v>
+      </c>
+      <c r="AC21" s="5">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A22" s="5">
+        <v>211</v>
+      </c>
+      <c r="B22" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="C22" s="4">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="D22" s="4">
+        <v>212</v>
+      </c>
+      <c r="E22" s="5">
+        <v>213</v>
+      </c>
+      <c r="G22" s="5">
+        <v>221</v>
+      </c>
+      <c r="H22" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I22" s="4">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="J22" s="4">
+        <v>222</v>
+      </c>
+      <c r="K22" s="5">
+        <v>223</v>
+      </c>
+      <c r="M22" s="5">
+        <v>231</v>
+      </c>
+      <c r="N22" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="O22" s="4">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="P22" s="4">
+        <v>232</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>233</v>
+      </c>
+      <c r="S22" s="5">
+        <v>241</v>
+      </c>
+      <c r="T22" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="U22" s="4">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="V22" s="4">
+        <v>242</v>
+      </c>
+      <c r="W22" s="5">
+        <v>243</v>
+      </c>
+      <c r="Y22" s="5">
+        <v>251</v>
+      </c>
+      <c r="Z22" s="5">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AA22" s="4">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="AB22" s="4">
+        <v>252</v>
+      </c>
+      <c r="AC22" s="5">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A26" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="G26" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="M26" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="N26" s="12"/>
+      <c r="O26" s="12"/>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="12"/>
+      <c r="S26" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="T26" s="12"/>
+      <c r="U26" s="12"/>
+      <c r="V26" s="12"/>
+      <c r="W26" s="12"/>
+      <c r="Y26" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z26" s="12"/>
+      <c r="AA26" s="12"/>
+      <c r="AB26" s="12"/>
+      <c r="AC26" s="12"/>
+    </row>
+    <row r="27" spans="1:29" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="U27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="W27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC27" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A28" s="5">
+        <v>311</v>
+      </c>
+      <c r="B28" s="5">
+        <f t="shared" ref="B28:C31" si="9">B10</f>
+        <v>1</v>
+      </c>
+      <c r="C28" s="4">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="D28" s="4">
+        <v>312</v>
+      </c>
+      <c r="E28" s="5">
+        <v>313</v>
+      </c>
+      <c r="G28" s="5">
+        <v>321</v>
+      </c>
+      <c r="H28" s="5">
+        <f t="shared" ref="H28:I31" si="10">B10</f>
+        <v>1</v>
+      </c>
+      <c r="I28" s="4">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="J28" s="4">
+        <v>322</v>
+      </c>
+      <c r="K28" s="5">
+        <v>323</v>
+      </c>
+      <c r="M28" s="5">
+        <v>331</v>
+      </c>
+      <c r="N28" s="5">
+        <f t="shared" ref="N28:O31" si="11">B10</f>
+        <v>1</v>
+      </c>
+      <c r="O28" s="4">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="P28" s="4">
+        <v>332</v>
+      </c>
+      <c r="Q28" s="5">
+        <v>333</v>
+      </c>
+      <c r="S28" s="5">
+        <v>341</v>
+      </c>
+      <c r="T28" s="5">
+        <f t="shared" ref="T28:U31" si="12">B10</f>
+        <v>1</v>
+      </c>
+      <c r="U28" s="4">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="V28" s="4">
+        <v>342</v>
+      </c>
+      <c r="W28" s="5">
+        <v>343</v>
+      </c>
+      <c r="Y28" s="5">
+        <v>351</v>
+      </c>
+      <c r="Z28" s="5">
+        <f t="shared" ref="Z28:AA31" si="13">B10</f>
+        <v>1</v>
+      </c>
+      <c r="AA28" s="4">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="AB28" s="4">
+        <v>352</v>
+      </c>
+      <c r="AC28" s="5">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A29" s="5">
+        <v>311</v>
+      </c>
+      <c r="B29" s="5">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="C29" s="4">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="D29" s="4">
+        <v>312</v>
+      </c>
+      <c r="E29" s="5">
+        <v>313</v>
+      </c>
+      <c r="G29" s="5">
+        <v>321</v>
+      </c>
+      <c r="H29" s="5">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="I29" s="4">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="J29" s="4">
+        <v>322</v>
+      </c>
+      <c r="K29" s="5">
+        <v>323</v>
+      </c>
+      <c r="M29" s="5">
+        <v>331</v>
+      </c>
+      <c r="N29" s="5">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="O29" s="4">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="P29" s="4">
+        <v>332</v>
+      </c>
+      <c r="Q29" s="5">
+        <v>333</v>
+      </c>
+      <c r="S29" s="5">
+        <v>341</v>
+      </c>
+      <c r="T29" s="5">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="U29" s="4">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="V29" s="4">
+        <v>342</v>
+      </c>
+      <c r="W29" s="5">
+        <v>343</v>
+      </c>
+      <c r="Y29" s="5">
+        <v>351</v>
+      </c>
+      <c r="Z29" s="5">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AA29" s="4">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="AB29" s="4">
+        <v>352</v>
+      </c>
+      <c r="AC29" s="5">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A30" s="5">
+        <v>311</v>
+      </c>
+      <c r="B30" s="5">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="C30" s="4">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="D30" s="4">
+        <v>312</v>
+      </c>
+      <c r="E30" s="5">
+        <v>313</v>
+      </c>
+      <c r="G30" s="5">
+        <v>321</v>
+      </c>
+      <c r="H30" s="5">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="I30" s="4">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="J30" s="4">
+        <v>322</v>
+      </c>
+      <c r="K30" s="5">
+        <v>323</v>
+      </c>
+      <c r="M30" s="5">
+        <v>331</v>
+      </c>
+      <c r="N30" s="5">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="O30" s="4">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="P30" s="4">
+        <v>332</v>
+      </c>
+      <c r="Q30" s="5">
+        <v>333</v>
+      </c>
+      <c r="S30" s="5">
+        <v>341</v>
+      </c>
+      <c r="T30" s="5">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="U30" s="4">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="V30" s="4">
+        <v>342</v>
+      </c>
+      <c r="W30" s="5">
+        <v>343</v>
+      </c>
+      <c r="Y30" s="5">
+        <v>351</v>
+      </c>
+      <c r="Z30" s="5">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AA30" s="4">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="AB30" s="4">
+        <v>352</v>
+      </c>
+      <c r="AC30" s="5">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A31" s="5">
+        <v>311</v>
+      </c>
+      <c r="B31" s="5">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="C31" s="4">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="D31" s="4">
+        <v>312</v>
+      </c>
+      <c r="E31" s="5">
+        <v>313</v>
+      </c>
+      <c r="G31" s="5">
+        <v>321</v>
+      </c>
+      <c r="H31" s="5">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="I31" s="4">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="J31" s="4">
+        <v>322</v>
+      </c>
+      <c r="K31" s="5">
+        <v>323</v>
+      </c>
+      <c r="M31" s="5">
+        <v>331</v>
+      </c>
+      <c r="N31" s="5">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="O31" s="4">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="P31" s="4">
+        <v>332</v>
+      </c>
+      <c r="Q31" s="5">
+        <v>333</v>
+      </c>
+      <c r="S31" s="5">
+        <v>341</v>
+      </c>
+      <c r="T31" s="5">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="U31" s="4">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="V31" s="4">
+        <v>342</v>
+      </c>
+      <c r="W31" s="5">
+        <v>343</v>
+      </c>
+      <c r="Y31" s="5">
+        <v>351</v>
+      </c>
+      <c r="Z31" s="5">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AA31" s="4">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="AB31" s="4">
+        <v>352</v>
+      </c>
+      <c r="AC31" s="5">
+        <v>353</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="Y8:AC8"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="G26:K26"/>
+    <mergeCell ref="M26:Q26"/>
+    <mergeCell ref="Y26:AC26"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="S26:W26"/>
+    <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="G17:K17"/>
+    <mergeCell ref="S17:W17"/>
+    <mergeCell ref="Y17:AC17"/>
+    <mergeCell ref="M17:Q17"/>
+    <mergeCell ref="S8:W8"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Pradiniai.xlsx
+++ b/Pradiniai.xlsx
@@ -2391,4 +2391,291 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumentas" ma:contentTypeID="0x010100BAB57CF81AE55C4698AAD22D302297F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Kurkite naują dokumentą." ma:contentTypeScope="" ma:versionID="49ab401eb4052690d2a2629974c22fd6">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="453e7e53-5eb2-45cf-b2ab-34c867e554b8" xmlns:ns3="aa0d983d-359a-438c-9953-3af1a8ac0831" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab9969d50e0b13c63bc5bd0499c928dc" ns2:_="" ns3:_="">
+    <xsd:import namespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
+    <xsd:import namespace="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="15" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="16" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Vaizdų žymės" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="993cf2ba-b7a7-49f7-97d1-76e12a88c412" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="23" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="aa0d983d-359a-438c-9953-3af1a8ac0831" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{82c4fa3c-500e-4213-91e5-1b9e2014ea63}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="aa0d983d-359a-438c-9953-3af1a8ac0831">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="21" nillable="true" ma:displayName="Bendrinama su" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="22" nillable="true" ma:displayName="Bendrinta su išsamia informacija" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Turinio tipas"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Antraštė"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="453e7e53-5eb2-45cf-b2ab-34c867e554b8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="aa0d983d-359a-438c-9953-3af1a8ac0831" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ED4B271-E36E-4423-9AD8-8A7D6411E1A1}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEAF7B52-4FEB-4740-BC25-5EF56EDEA0FB}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF92B90-5FA6-4A72-98B0-AE6016D11637}"/>
 </file>
--- a/Pradiniai.xlsx
+++ b/Pradiniai.xlsx
@@ -622,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A5:G9"/>
+  <dimension ref="A5:FE12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="15" customWidth="1" style="12" min="1" max="5"/>
@@ -632,6 +632,160 @@
     <col width="15" customWidth="1" style="12" min="5" max="5"/>
     <col width="18" customWidth="1" style="12" min="6" max="7"/>
     <col width="18" customWidth="1" style="12" min="7" max="7"/>
+    <col width="15" customWidth="1" style="12" min="8" max="8"/>
+    <col width="15" customWidth="1" style="12" min="9" max="9"/>
+    <col width="15" customWidth="1" style="12" min="10" max="10"/>
+    <col width="15" customWidth="1" style="12" min="11" max="11"/>
+    <col width="15" customWidth="1" style="12" min="12" max="12"/>
+    <col width="15" customWidth="1" style="12" min="13" max="13"/>
+    <col width="15" customWidth="1" style="12" min="14" max="14"/>
+    <col width="15" customWidth="1" style="12" min="15" max="15"/>
+    <col width="15" customWidth="1" style="12" min="16" max="16"/>
+    <col width="15" customWidth="1" style="12" min="17" max="17"/>
+    <col width="15" customWidth="1" style="12" min="18" max="18"/>
+    <col width="15" customWidth="1" style="12" min="19" max="19"/>
+    <col width="15" customWidth="1" style="12" min="20" max="20"/>
+    <col width="15" customWidth="1" style="12" min="21" max="21"/>
+    <col width="15" customWidth="1" style="12" min="22" max="22"/>
+    <col width="15" customWidth="1" style="12" min="23" max="23"/>
+    <col width="15" customWidth="1" style="12" min="24" max="24"/>
+    <col width="15" customWidth="1" style="12" min="25" max="25"/>
+    <col width="15" customWidth="1" style="12" min="26" max="26"/>
+    <col width="15" customWidth="1" style="12" min="27" max="27"/>
+    <col width="15" customWidth="1" style="12" min="28" max="28"/>
+    <col width="15" customWidth="1" style="12" min="29" max="29"/>
+    <col width="15" customWidth="1" style="12" min="30" max="30"/>
+    <col width="15" customWidth="1" style="12" min="31" max="31"/>
+    <col width="15" customWidth="1" style="12" min="32" max="32"/>
+    <col width="15" customWidth="1" style="12" min="33" max="33"/>
+    <col width="15" customWidth="1" style="12" min="34" max="34"/>
+    <col width="15" customWidth="1" style="12" min="35" max="35"/>
+    <col width="15" customWidth="1" style="12" min="36" max="36"/>
+    <col width="15" customWidth="1" style="12" min="37" max="37"/>
+    <col width="15" customWidth="1" style="12" min="38" max="38"/>
+    <col width="15" customWidth="1" style="12" min="39" max="39"/>
+    <col width="15" customWidth="1" style="12" min="40" max="40"/>
+    <col width="15" customWidth="1" style="12" min="41" max="41"/>
+    <col width="15" customWidth="1" style="12" min="42" max="42"/>
+    <col width="15" customWidth="1" style="12" min="43" max="43"/>
+    <col width="15" customWidth="1" style="12" min="44" max="44"/>
+    <col width="15" customWidth="1" style="12" min="45" max="45"/>
+    <col width="15" customWidth="1" style="12" min="46" max="46"/>
+    <col width="15" customWidth="1" style="12" min="47" max="47"/>
+    <col width="15" customWidth="1" style="12" min="48" max="48"/>
+    <col width="15" customWidth="1" style="12" min="49" max="49"/>
+    <col width="15" customWidth="1" style="12" min="50" max="50"/>
+    <col width="15" customWidth="1" style="12" min="51" max="51"/>
+    <col width="15" customWidth="1" style="12" min="52" max="52"/>
+    <col width="15" customWidth="1" style="12" min="53" max="53"/>
+    <col width="15" customWidth="1" style="12" min="54" max="54"/>
+    <col width="15" customWidth="1" style="12" min="55" max="55"/>
+    <col width="15" customWidth="1" style="12" min="56" max="56"/>
+    <col width="15" customWidth="1" style="12" min="57" max="57"/>
+    <col width="15" customWidth="1" style="12" min="58" max="58"/>
+    <col width="15" customWidth="1" style="12" min="59" max="59"/>
+    <col width="15" customWidth="1" style="12" min="60" max="60"/>
+    <col width="15" customWidth="1" style="12" min="61" max="61"/>
+    <col width="15" customWidth="1" style="12" min="62" max="62"/>
+    <col width="15" customWidth="1" style="12" min="63" max="63"/>
+    <col width="15" customWidth="1" style="12" min="64" max="64"/>
+    <col width="15" customWidth="1" style="12" min="65" max="65"/>
+    <col width="15" customWidth="1" style="12" min="66" max="66"/>
+    <col width="15" customWidth="1" style="12" min="67" max="67"/>
+    <col width="15" customWidth="1" style="12" min="68" max="68"/>
+    <col width="15" customWidth="1" style="12" min="69" max="69"/>
+    <col width="15" customWidth="1" style="12" min="70" max="70"/>
+    <col width="15" customWidth="1" style="12" min="71" max="71"/>
+    <col width="15" customWidth="1" style="12" min="72" max="72"/>
+    <col width="15" customWidth="1" style="12" min="73" max="73"/>
+    <col width="15" customWidth="1" style="12" min="74" max="74"/>
+    <col width="15" customWidth="1" style="12" min="75" max="75"/>
+    <col width="15" customWidth="1" style="12" min="76" max="76"/>
+    <col width="15" customWidth="1" style="12" min="77" max="77"/>
+    <col width="15" customWidth="1" style="12" min="78" max="78"/>
+    <col width="15" customWidth="1" style="12" min="79" max="79"/>
+    <col width="15" customWidth="1" style="12" min="80" max="80"/>
+    <col width="15" customWidth="1" style="12" min="81" max="81"/>
+    <col width="15" customWidth="1" style="12" min="82" max="82"/>
+    <col width="15" customWidth="1" style="12" min="83" max="83"/>
+    <col width="15" customWidth="1" style="12" min="84" max="84"/>
+    <col width="15" customWidth="1" style="12" min="85" max="85"/>
+    <col width="15" customWidth="1" style="12" min="86" max="86"/>
+    <col width="15" customWidth="1" style="12" min="87" max="87"/>
+    <col width="15" customWidth="1" style="12" min="88" max="88"/>
+    <col width="15" customWidth="1" style="12" min="89" max="89"/>
+    <col width="15" customWidth="1" style="12" min="90" max="90"/>
+    <col width="15" customWidth="1" style="12" min="91" max="91"/>
+    <col width="15" customWidth="1" style="12" min="92" max="92"/>
+    <col width="15" customWidth="1" style="12" min="93" max="93"/>
+    <col width="15" customWidth="1" style="12" min="94" max="94"/>
+    <col width="15" customWidth="1" style="12" min="95" max="95"/>
+    <col width="15" customWidth="1" style="12" min="96" max="96"/>
+    <col width="15" customWidth="1" style="12" min="97" max="97"/>
+    <col width="15" customWidth="1" style="12" min="98" max="98"/>
+    <col width="15" customWidth="1" style="12" min="99" max="99"/>
+    <col width="15" customWidth="1" style="12" min="100" max="100"/>
+    <col width="15" customWidth="1" style="12" min="101" max="101"/>
+    <col width="15" customWidth="1" style="12" min="102" max="102"/>
+    <col width="15" customWidth="1" style="12" min="103" max="103"/>
+    <col width="15" customWidth="1" style="12" min="104" max="104"/>
+    <col width="15" customWidth="1" style="12" min="105" max="105"/>
+    <col width="15" customWidth="1" style="12" min="106" max="106"/>
+    <col width="15" customWidth="1" style="12" min="107" max="107"/>
+    <col width="15" customWidth="1" style="12" min="108" max="108"/>
+    <col width="15" customWidth="1" style="12" min="109" max="109"/>
+    <col width="15" customWidth="1" style="12" min="110" max="110"/>
+    <col width="15" customWidth="1" style="12" min="111" max="111"/>
+    <col width="15" customWidth="1" style="12" min="112" max="112"/>
+    <col width="15" customWidth="1" style="12" min="113" max="113"/>
+    <col width="15" customWidth="1" style="12" min="114" max="114"/>
+    <col width="15" customWidth="1" style="12" min="115" max="115"/>
+    <col width="15" customWidth="1" style="12" min="116" max="116"/>
+    <col width="15" customWidth="1" style="12" min="117" max="117"/>
+    <col width="15" customWidth="1" style="12" min="118" max="118"/>
+    <col width="15" customWidth="1" style="12" min="119" max="119"/>
+    <col width="15" customWidth="1" style="12" min="120" max="120"/>
+    <col width="15" customWidth="1" style="12" min="121" max="121"/>
+    <col width="15" customWidth="1" style="12" min="122" max="122"/>
+    <col width="15" customWidth="1" style="12" min="123" max="123"/>
+    <col width="15" customWidth="1" style="12" min="124" max="124"/>
+    <col width="15" customWidth="1" style="12" min="125" max="125"/>
+    <col width="15" customWidth="1" style="12" min="126" max="126"/>
+    <col width="15" customWidth="1" style="12" min="127" max="127"/>
+    <col width="15" customWidth="1" style="12" min="128" max="128"/>
+    <col width="15" customWidth="1" style="12" min="129" max="129"/>
+    <col width="15" customWidth="1" style="12" min="130" max="130"/>
+    <col width="15" customWidth="1" style="12" min="131" max="131"/>
+    <col width="15" customWidth="1" style="12" min="132" max="132"/>
+    <col width="15" customWidth="1" style="12" min="133" max="133"/>
+    <col width="15" customWidth="1" style="12" min="134" max="134"/>
+    <col width="15" customWidth="1" style="12" min="135" max="135"/>
+    <col width="15" customWidth="1" style="12" min="136" max="136"/>
+    <col width="15" customWidth="1" style="12" min="137" max="137"/>
+    <col width="15" customWidth="1" style="12" min="138" max="138"/>
+    <col width="15" customWidth="1" style="12" min="139" max="139"/>
+    <col width="15" customWidth="1" style="12" min="140" max="140"/>
+    <col width="15" customWidth="1" style="12" min="141" max="141"/>
+    <col width="15" customWidth="1" style="12" min="142" max="142"/>
+    <col width="15" customWidth="1" style="12" min="143" max="143"/>
+    <col width="15" customWidth="1" style="12" min="144" max="144"/>
+    <col width="15" customWidth="1" style="12" min="145" max="145"/>
+    <col width="15" customWidth="1" style="12" min="146" max="146"/>
+    <col width="15" customWidth="1" style="12" min="147" max="147"/>
+    <col width="15" customWidth="1" style="12" min="148" max="148"/>
+    <col width="15" customWidth="1" style="12" min="149" max="149"/>
+    <col width="15" customWidth="1" style="12" min="150" max="150"/>
+    <col width="15" customWidth="1" style="12" min="151" max="151"/>
+    <col width="15" customWidth="1" style="12" min="152" max="152"/>
+    <col width="15" customWidth="1" style="12" min="153" max="153"/>
+    <col width="15" customWidth="1" style="12" min="154" max="154"/>
+    <col width="15" customWidth="1" style="12" min="155" max="155"/>
+    <col width="15" customWidth="1" style="12" min="156" max="156"/>
+    <col width="15" customWidth="1" style="12" min="157" max="157"/>
+    <col width="15" customWidth="1" style="12" min="158" max="158"/>
+    <col width="15" customWidth="1" style="12" min="159" max="159"/>
+    <col width="18" customWidth="1" style="12" min="160" max="160"/>
+    <col width="18" customWidth="1" style="12" min="161" max="161"/>
   </cols>
   <sheetData>
     <row r="5" ht="58" customHeight="1" s="12">
@@ -670,6 +824,776 @@
           <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
         </is>
       </c>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 8 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 9 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 10 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="K5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 11 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="L5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 12 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="M5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 13 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="N5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 14 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="O5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 15 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="P5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 16 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="Q5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 17 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="R5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 18 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="S5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 19 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="T5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 20 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="U5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 21 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="V5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 22 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="W5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 23 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="X5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 24 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="Y5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 25 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="Z5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 26 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AA5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 27 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AB5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 28 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AC5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 29 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AD5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 30 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AE5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 31 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AF5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 32 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AG5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 33 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AH5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 34 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AI5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 35 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AJ5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 36 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AK5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 37 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AL5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 38 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AM5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 39 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AN5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 40 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AO5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 41 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AP5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 42 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AQ5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 43 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AR5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 44 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AS5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 45 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AT5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 46 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AU5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 47 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AV5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 48 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AW5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 49 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AX5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 50 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AY5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 51 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="AZ5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 52 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BA5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 53 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BB5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 54 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BC5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 55 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BD5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 56 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BE5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 57 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BF5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 58 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BG5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 59 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BH5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 60 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BI5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 61 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BJ5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 62 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BK5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 63 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BL5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 64 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BM5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 65 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BN5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 66 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BO5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 67 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BP5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 68 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BQ5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 69 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BR5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 70 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BS5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 71 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BT5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 72 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BU5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 73 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BV5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 74 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BW5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 75 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BX5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 76 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BY5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 77 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="BZ5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 78 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CA5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 79 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CB5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 80 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CC5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 81 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CD5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 82 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CE5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 83 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CF5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 84 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CG5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 85 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CH5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 86 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CI5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 87 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CJ5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 88 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CK5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 89 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CL5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 90 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CM5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 91 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CN5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 92 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CO5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 93 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CP5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 94 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CQ5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 95 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CR5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 96 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CS5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 97 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CT5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 98 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CU5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 99 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CV5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 100 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CW5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 101 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CX5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 102 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CY5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 103 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="CZ5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 104 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DA5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 105 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DB5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 106 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DC5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 107 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DD5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 108 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DE5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 109 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DF5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 110 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DG5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 111 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DH5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 112 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DI5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 113 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DJ5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 114 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DK5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 115 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DL5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 116 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DM5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 117 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DN5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 118 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DO5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 119 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DP5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 120 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DQ5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 121 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DR5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 122 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DS5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 123 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DT5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 124 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DU5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 125 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DV5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 126 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DW5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 127 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DX5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 128 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DY5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 129 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="DZ5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 130 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EA5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 131 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EB5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 132 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EC5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 133 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="ED5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 134 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EE5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 135 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EF5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 136 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EG5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 137 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EH5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 138 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EI5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 139 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EJ5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 140 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EK5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 141 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EL5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 142 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EM5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 143 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EN5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 144 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EO5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 145 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EP5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 146 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EQ5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 147 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="ER5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 148 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="ES5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 149 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="ET5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 150 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EU5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 151 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EV5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 152 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EW5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 153 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EX5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 154 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EY5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 155 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="EZ5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 156 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="FA5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 157 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="FB5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 158 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="FC5" s="16" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 159 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="FD5" s="16" t="inlineStr">
+        <is>
+          <t>Atmosferinis slėgis P, hPa</t>
+        </is>
+      </c>
+      <c r="FE5" s="16" t="inlineStr">
+        <is>
+          <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="n">
@@ -693,6 +1617,160 @@
       <c r="G6" s="17" t="n">
         <v>-0.25</v>
       </c>
+      <c r="H6" s="17" t="n"/>
+      <c r="I6" s="17" t="n"/>
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="17" t="n"/>
+      <c r="O6" s="17" t="n"/>
+      <c r="P6" s="17" t="n"/>
+      <c r="Q6" s="17" t="n"/>
+      <c r="R6" s="17" t="n"/>
+      <c r="S6" s="17" t="n"/>
+      <c r="T6" s="17" t="n"/>
+      <c r="U6" s="17" t="n"/>
+      <c r="V6" s="17" t="n"/>
+      <c r="W6" s="17" t="n"/>
+      <c r="X6" s="17" t="n"/>
+      <c r="Y6" s="17" t="n"/>
+      <c r="Z6" s="17" t="n"/>
+      <c r="AA6" s="17" t="n"/>
+      <c r="AB6" s="17" t="n"/>
+      <c r="AC6" s="17" t="n"/>
+      <c r="AD6" s="17" t="n"/>
+      <c r="AE6" s="17" t="n"/>
+      <c r="AF6" s="17" t="n"/>
+      <c r="AG6" s="17" t="n"/>
+      <c r="AH6" s="17" t="n"/>
+      <c r="AI6" s="17" t="n"/>
+      <c r="AJ6" s="17" t="n"/>
+      <c r="AK6" s="17" t="n"/>
+      <c r="AL6" s="17" t="n"/>
+      <c r="AM6" s="17" t="n"/>
+      <c r="AN6" s="17" t="n"/>
+      <c r="AO6" s="17" t="n"/>
+      <c r="AP6" s="17" t="n"/>
+      <c r="AQ6" s="17" t="n"/>
+      <c r="AR6" s="17" t="n"/>
+      <c r="AS6" s="17" t="n"/>
+      <c r="AT6" s="17" t="n"/>
+      <c r="AU6" s="17" t="n"/>
+      <c r="AV6" s="17" t="n"/>
+      <c r="AW6" s="17" t="n"/>
+      <c r="AX6" s="17" t="n"/>
+      <c r="AY6" s="17" t="n"/>
+      <c r="AZ6" s="17" t="n"/>
+      <c r="BA6" s="17" t="n"/>
+      <c r="BB6" s="17" t="n"/>
+      <c r="BC6" s="17" t="n"/>
+      <c r="BD6" s="17" t="n"/>
+      <c r="BE6" s="17" t="n"/>
+      <c r="BF6" s="17" t="n"/>
+      <c r="BG6" s="17" t="n"/>
+      <c r="BH6" s="17" t="n"/>
+      <c r="BI6" s="17" t="n"/>
+      <c r="BJ6" s="17" t="n"/>
+      <c r="BK6" s="17" t="n"/>
+      <c r="BL6" s="17" t="n"/>
+      <c r="BM6" s="17" t="n"/>
+      <c r="BN6" s="17" t="n"/>
+      <c r="BO6" s="17" t="n"/>
+      <c r="BP6" s="17" t="n"/>
+      <c r="BQ6" s="17" t="n"/>
+      <c r="BR6" s="17" t="n"/>
+      <c r="BS6" s="17" t="n"/>
+      <c r="BT6" s="17" t="n"/>
+      <c r="BU6" s="17" t="n"/>
+      <c r="BV6" s="17" t="n"/>
+      <c r="BW6" s="17" t="n"/>
+      <c r="BX6" s="17" t="n"/>
+      <c r="BY6" s="17" t="n"/>
+      <c r="BZ6" s="17" t="n"/>
+      <c r="CA6" s="17" t="n"/>
+      <c r="CB6" s="17" t="n"/>
+      <c r="CC6" s="17" t="n"/>
+      <c r="CD6" s="17" t="n"/>
+      <c r="CE6" s="17" t="n"/>
+      <c r="CF6" s="17" t="n"/>
+      <c r="CG6" s="17" t="n"/>
+      <c r="CH6" s="17" t="n"/>
+      <c r="CI6" s="17" t="n"/>
+      <c r="CJ6" s="17" t="n"/>
+      <c r="CK6" s="17" t="n"/>
+      <c r="CL6" s="17" t="n"/>
+      <c r="CM6" s="17" t="n"/>
+      <c r="CN6" s="17" t="n"/>
+      <c r="CO6" s="17" t="n"/>
+      <c r="CP6" s="17" t="n"/>
+      <c r="CQ6" s="17" t="n"/>
+      <c r="CR6" s="17" t="n"/>
+      <c r="CS6" s="17" t="n"/>
+      <c r="CT6" s="17" t="n"/>
+      <c r="CU6" s="17" t="n"/>
+      <c r="CV6" s="17" t="n"/>
+      <c r="CW6" s="17" t="n"/>
+      <c r="CX6" s="17" t="n"/>
+      <c r="CY6" s="17" t="n"/>
+      <c r="CZ6" s="17" t="n"/>
+      <c r="DA6" s="17" t="n"/>
+      <c r="DB6" s="17" t="n"/>
+      <c r="DC6" s="17" t="n"/>
+      <c r="DD6" s="17" t="n"/>
+      <c r="DE6" s="17" t="n"/>
+      <c r="DF6" s="17" t="n"/>
+      <c r="DG6" s="17" t="n"/>
+      <c r="DH6" s="17" t="n"/>
+      <c r="DI6" s="17" t="n"/>
+      <c r="DJ6" s="17" t="n"/>
+      <c r="DK6" s="17" t="n"/>
+      <c r="DL6" s="17" t="n"/>
+      <c r="DM6" s="17" t="n"/>
+      <c r="DN6" s="17" t="n"/>
+      <c r="DO6" s="17" t="n"/>
+      <c r="DP6" s="17" t="n"/>
+      <c r="DQ6" s="17" t="n"/>
+      <c r="DR6" s="17" t="n"/>
+      <c r="DS6" s="17" t="n"/>
+      <c r="DT6" s="17" t="n"/>
+      <c r="DU6" s="17" t="n"/>
+      <c r="DV6" s="17" t="n"/>
+      <c r="DW6" s="17" t="n"/>
+      <c r="DX6" s="17" t="n"/>
+      <c r="DY6" s="17" t="n"/>
+      <c r="DZ6" s="17" t="n"/>
+      <c r="EA6" s="17" t="n"/>
+      <c r="EB6" s="17" t="n"/>
+      <c r="EC6" s="17" t="n"/>
+      <c r="ED6" s="17" t="n"/>
+      <c r="EE6" s="17" t="n"/>
+      <c r="EF6" s="17" t="n"/>
+      <c r="EG6" s="17" t="n"/>
+      <c r="EH6" s="17" t="n"/>
+      <c r="EI6" s="17" t="n"/>
+      <c r="EJ6" s="17" t="n"/>
+      <c r="EK6" s="17" t="n"/>
+      <c r="EL6" s="17" t="n"/>
+      <c r="EM6" s="17" t="n"/>
+      <c r="EN6" s="17" t="n"/>
+      <c r="EO6" s="17" t="n"/>
+      <c r="EP6" s="17" t="n"/>
+      <c r="EQ6" s="17" t="n"/>
+      <c r="ER6" s="17" t="n"/>
+      <c r="ES6" s="17" t="n"/>
+      <c r="ET6" s="17" t="n"/>
+      <c r="EU6" s="17" t="n"/>
+      <c r="EV6" s="17" t="n"/>
+      <c r="EW6" s="17" t="n"/>
+      <c r="EX6" s="17" t="n"/>
+      <c r="EY6" s="17" t="n"/>
+      <c r="EZ6" s="17" t="n"/>
+      <c r="FA6" s="17" t="n"/>
+      <c r="FB6" s="17" t="n"/>
+      <c r="FC6" s="17" t="n"/>
+      <c r="FD6" s="18" t="n"/>
+      <c r="FE6" s="17" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="17" t="n">
@@ -712,6 +1790,160 @@
       </c>
       <c r="F7" s="19" t="n"/>
       <c r="G7" s="19" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
+      <c r="Q7" s="17" t="n"/>
+      <c r="R7" s="17" t="n"/>
+      <c r="S7" s="17" t="n"/>
+      <c r="T7" s="17" t="n"/>
+      <c r="U7" s="17" t="n"/>
+      <c r="V7" s="17" t="n"/>
+      <c r="W7" s="17" t="n"/>
+      <c r="X7" s="17" t="n"/>
+      <c r="Y7" s="17" t="n"/>
+      <c r="Z7" s="17" t="n"/>
+      <c r="AA7" s="17" t="n"/>
+      <c r="AB7" s="17" t="n"/>
+      <c r="AC7" s="17" t="n"/>
+      <c r="AD7" s="17" t="n"/>
+      <c r="AE7" s="17" t="n"/>
+      <c r="AF7" s="17" t="n"/>
+      <c r="AG7" s="17" t="n"/>
+      <c r="AH7" s="17" t="n"/>
+      <c r="AI7" s="17" t="n"/>
+      <c r="AJ7" s="17" t="n"/>
+      <c r="AK7" s="17" t="n"/>
+      <c r="AL7" s="17" t="n"/>
+      <c r="AM7" s="17" t="n"/>
+      <c r="AN7" s="17" t="n"/>
+      <c r="AO7" s="17" t="n"/>
+      <c r="AP7" s="17" t="n"/>
+      <c r="AQ7" s="17" t="n"/>
+      <c r="AR7" s="17" t="n"/>
+      <c r="AS7" s="17" t="n"/>
+      <c r="AT7" s="17" t="n"/>
+      <c r="AU7" s="17" t="n"/>
+      <c r="AV7" s="17" t="n"/>
+      <c r="AW7" s="17" t="n"/>
+      <c r="AX7" s="17" t="n"/>
+      <c r="AY7" s="17" t="n"/>
+      <c r="AZ7" s="17" t="n"/>
+      <c r="BA7" s="17" t="n"/>
+      <c r="BB7" s="17" t="n"/>
+      <c r="BC7" s="17" t="n"/>
+      <c r="BD7" s="17" t="n"/>
+      <c r="BE7" s="17" t="n"/>
+      <c r="BF7" s="17" t="n"/>
+      <c r="BG7" s="17" t="n"/>
+      <c r="BH7" s="17" t="n"/>
+      <c r="BI7" s="17" t="n"/>
+      <c r="BJ7" s="17" t="n"/>
+      <c r="BK7" s="17" t="n"/>
+      <c r="BL7" s="17" t="n"/>
+      <c r="BM7" s="17" t="n"/>
+      <c r="BN7" s="17" t="n"/>
+      <c r="BO7" s="17" t="n"/>
+      <c r="BP7" s="17" t="n"/>
+      <c r="BQ7" s="17" t="n"/>
+      <c r="BR7" s="17" t="n"/>
+      <c r="BS7" s="17" t="n"/>
+      <c r="BT7" s="17" t="n"/>
+      <c r="BU7" s="17" t="n"/>
+      <c r="BV7" s="17" t="n"/>
+      <c r="BW7" s="17" t="n"/>
+      <c r="BX7" s="17" t="n"/>
+      <c r="BY7" s="17" t="n"/>
+      <c r="BZ7" s="17" t="n"/>
+      <c r="CA7" s="17" t="n"/>
+      <c r="CB7" s="17" t="n"/>
+      <c r="CC7" s="17" t="n"/>
+      <c r="CD7" s="17" t="n"/>
+      <c r="CE7" s="17" t="n"/>
+      <c r="CF7" s="17" t="n"/>
+      <c r="CG7" s="17" t="n"/>
+      <c r="CH7" s="17" t="n"/>
+      <c r="CI7" s="17" t="n"/>
+      <c r="CJ7" s="17" t="n"/>
+      <c r="CK7" s="17" t="n"/>
+      <c r="CL7" s="17" t="n"/>
+      <c r="CM7" s="17" t="n"/>
+      <c r="CN7" s="17" t="n"/>
+      <c r="CO7" s="17" t="n"/>
+      <c r="CP7" s="17" t="n"/>
+      <c r="CQ7" s="17" t="n"/>
+      <c r="CR7" s="17" t="n"/>
+      <c r="CS7" s="17" t="n"/>
+      <c r="CT7" s="17" t="n"/>
+      <c r="CU7" s="17" t="n"/>
+      <c r="CV7" s="17" t="n"/>
+      <c r="CW7" s="17" t="n"/>
+      <c r="CX7" s="17" t="n"/>
+      <c r="CY7" s="17" t="n"/>
+      <c r="CZ7" s="17" t="n"/>
+      <c r="DA7" s="17" t="n"/>
+      <c r="DB7" s="17" t="n"/>
+      <c r="DC7" s="17" t="n"/>
+      <c r="DD7" s="17" t="n"/>
+      <c r="DE7" s="17" t="n"/>
+      <c r="DF7" s="17" t="n"/>
+      <c r="DG7" s="17" t="n"/>
+      <c r="DH7" s="17" t="n"/>
+      <c r="DI7" s="17" t="n"/>
+      <c r="DJ7" s="17" t="n"/>
+      <c r="DK7" s="17" t="n"/>
+      <c r="DL7" s="17" t="n"/>
+      <c r="DM7" s="17" t="n"/>
+      <c r="DN7" s="17" t="n"/>
+      <c r="DO7" s="17" t="n"/>
+      <c r="DP7" s="17" t="n"/>
+      <c r="DQ7" s="17" t="n"/>
+      <c r="DR7" s="17" t="n"/>
+      <c r="DS7" s="17" t="n"/>
+      <c r="DT7" s="17" t="n"/>
+      <c r="DU7" s="17" t="n"/>
+      <c r="DV7" s="17" t="n"/>
+      <c r="DW7" s="17" t="n"/>
+      <c r="DX7" s="17" t="n"/>
+      <c r="DY7" s="17" t="n"/>
+      <c r="DZ7" s="17" t="n"/>
+      <c r="EA7" s="17" t="n"/>
+      <c r="EB7" s="17" t="n"/>
+      <c r="EC7" s="17" t="n"/>
+      <c r="ED7" s="17" t="n"/>
+      <c r="EE7" s="17" t="n"/>
+      <c r="EF7" s="17" t="n"/>
+      <c r="EG7" s="17" t="n"/>
+      <c r="EH7" s="17" t="n"/>
+      <c r="EI7" s="17" t="n"/>
+      <c r="EJ7" s="17" t="n"/>
+      <c r="EK7" s="17" t="n"/>
+      <c r="EL7" s="17" t="n"/>
+      <c r="EM7" s="17" t="n"/>
+      <c r="EN7" s="17" t="n"/>
+      <c r="EO7" s="17" t="n"/>
+      <c r="EP7" s="17" t="n"/>
+      <c r="EQ7" s="17" t="n"/>
+      <c r="ER7" s="17" t="n"/>
+      <c r="ES7" s="17" t="n"/>
+      <c r="ET7" s="17" t="n"/>
+      <c r="EU7" s="17" t="n"/>
+      <c r="EV7" s="17" t="n"/>
+      <c r="EW7" s="17" t="n"/>
+      <c r="EX7" s="17" t="n"/>
+      <c r="EY7" s="17" t="n"/>
+      <c r="EZ7" s="17" t="n"/>
+      <c r="FA7" s="17" t="n"/>
+      <c r="FB7" s="17" t="n"/>
+      <c r="FC7" s="17" t="n"/>
+      <c r="FD7" s="19" t="n"/>
+      <c r="FE7" s="19" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="17" t="n">
@@ -731,6 +1963,160 @@
       </c>
       <c r="F8" s="19" t="n"/>
       <c r="G8" s="19" t="n"/>
+      <c r="H8" s="17" t="n"/>
+      <c r="I8" s="17" t="n"/>
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="17" t="n"/>
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="17" t="n"/>
+      <c r="O8" s="17" t="n"/>
+      <c r="P8" s="17" t="n"/>
+      <c r="Q8" s="17" t="n"/>
+      <c r="R8" s="17" t="n"/>
+      <c r="S8" s="17" t="n"/>
+      <c r="T8" s="17" t="n"/>
+      <c r="U8" s="17" t="n"/>
+      <c r="V8" s="17" t="n"/>
+      <c r="W8" s="17" t="n"/>
+      <c r="X8" s="17" t="n"/>
+      <c r="Y8" s="17" t="n"/>
+      <c r="Z8" s="17" t="n"/>
+      <c r="AA8" s="17" t="n"/>
+      <c r="AB8" s="17" t="n"/>
+      <c r="AC8" s="17" t="n"/>
+      <c r="AD8" s="17" t="n"/>
+      <c r="AE8" s="17" t="n"/>
+      <c r="AF8" s="17" t="n"/>
+      <c r="AG8" s="17" t="n"/>
+      <c r="AH8" s="17" t="n"/>
+      <c r="AI8" s="17" t="n"/>
+      <c r="AJ8" s="17" t="n"/>
+      <c r="AK8" s="17" t="n"/>
+      <c r="AL8" s="17" t="n"/>
+      <c r="AM8" s="17" t="n"/>
+      <c r="AN8" s="17" t="n"/>
+      <c r="AO8" s="17" t="n"/>
+      <c r="AP8" s="17" t="n"/>
+      <c r="AQ8" s="17" t="n"/>
+      <c r="AR8" s="17" t="n"/>
+      <c r="AS8" s="17" t="n"/>
+      <c r="AT8" s="17" t="n"/>
+      <c r="AU8" s="17" t="n"/>
+      <c r="AV8" s="17" t="n"/>
+      <c r="AW8" s="17" t="n"/>
+      <c r="AX8" s="17" t="n"/>
+      <c r="AY8" s="17" t="n"/>
+      <c r="AZ8" s="17" t="n"/>
+      <c r="BA8" s="17" t="n"/>
+      <c r="BB8" s="17" t="n"/>
+      <c r="BC8" s="17" t="n"/>
+      <c r="BD8" s="17" t="n"/>
+      <c r="BE8" s="17" t="n"/>
+      <c r="BF8" s="17" t="n"/>
+      <c r="BG8" s="17" t="n"/>
+      <c r="BH8" s="17" t="n"/>
+      <c r="BI8" s="17" t="n"/>
+      <c r="BJ8" s="17" t="n"/>
+      <c r="BK8" s="17" t="n"/>
+      <c r="BL8" s="17" t="n"/>
+      <c r="BM8" s="17" t="n"/>
+      <c r="BN8" s="17" t="n"/>
+      <c r="BO8" s="17" t="n"/>
+      <c r="BP8" s="17" t="n"/>
+      <c r="BQ8" s="17" t="n"/>
+      <c r="BR8" s="17" t="n"/>
+      <c r="BS8" s="17" t="n"/>
+      <c r="BT8" s="17" t="n"/>
+      <c r="BU8" s="17" t="n"/>
+      <c r="BV8" s="17" t="n"/>
+      <c r="BW8" s="17" t="n"/>
+      <c r="BX8" s="17" t="n"/>
+      <c r="BY8" s="17" t="n"/>
+      <c r="BZ8" s="17" t="n"/>
+      <c r="CA8" s="17" t="n"/>
+      <c r="CB8" s="17" t="n"/>
+      <c r="CC8" s="17" t="n"/>
+      <c r="CD8" s="17" t="n"/>
+      <c r="CE8" s="17" t="n"/>
+      <c r="CF8" s="17" t="n"/>
+      <c r="CG8" s="17" t="n"/>
+      <c r="CH8" s="17" t="n"/>
+      <c r="CI8" s="17" t="n"/>
+      <c r="CJ8" s="17" t="n"/>
+      <c r="CK8" s="17" t="n"/>
+      <c r="CL8" s="17" t="n"/>
+      <c r="CM8" s="17" t="n"/>
+      <c r="CN8" s="17" t="n"/>
+      <c r="CO8" s="17" t="n"/>
+      <c r="CP8" s="17" t="n"/>
+      <c r="CQ8" s="17" t="n"/>
+      <c r="CR8" s="17" t="n"/>
+      <c r="CS8" s="17" t="n"/>
+      <c r="CT8" s="17" t="n"/>
+      <c r="CU8" s="17" t="n"/>
+      <c r="CV8" s="17" t="n"/>
+      <c r="CW8" s="17" t="n"/>
+      <c r="CX8" s="17" t="n"/>
+      <c r="CY8" s="17" t="n"/>
+      <c r="CZ8" s="17" t="n"/>
+      <c r="DA8" s="17" t="n"/>
+      <c r="DB8" s="17" t="n"/>
+      <c r="DC8" s="17" t="n"/>
+      <c r="DD8" s="17" t="n"/>
+      <c r="DE8" s="17" t="n"/>
+      <c r="DF8" s="17" t="n"/>
+      <c r="DG8" s="17" t="n"/>
+      <c r="DH8" s="17" t="n"/>
+      <c r="DI8" s="17" t="n"/>
+      <c r="DJ8" s="17" t="n"/>
+      <c r="DK8" s="17" t="n"/>
+      <c r="DL8" s="17" t="n"/>
+      <c r="DM8" s="17" t="n"/>
+      <c r="DN8" s="17" t="n"/>
+      <c r="DO8" s="17" t="n"/>
+      <c r="DP8" s="17" t="n"/>
+      <c r="DQ8" s="17" t="n"/>
+      <c r="DR8" s="17" t="n"/>
+      <c r="DS8" s="17" t="n"/>
+      <c r="DT8" s="17" t="n"/>
+      <c r="DU8" s="17" t="n"/>
+      <c r="DV8" s="17" t="n"/>
+      <c r="DW8" s="17" t="n"/>
+      <c r="DX8" s="17" t="n"/>
+      <c r="DY8" s="17" t="n"/>
+      <c r="DZ8" s="17" t="n"/>
+      <c r="EA8" s="17" t="n"/>
+      <c r="EB8" s="17" t="n"/>
+      <c r="EC8" s="17" t="n"/>
+      <c r="ED8" s="17" t="n"/>
+      <c r="EE8" s="17" t="n"/>
+      <c r="EF8" s="17" t="n"/>
+      <c r="EG8" s="17" t="n"/>
+      <c r="EH8" s="17" t="n"/>
+      <c r="EI8" s="17" t="n"/>
+      <c r="EJ8" s="17" t="n"/>
+      <c r="EK8" s="17" t="n"/>
+      <c r="EL8" s="17" t="n"/>
+      <c r="EM8" s="17" t="n"/>
+      <c r="EN8" s="17" t="n"/>
+      <c r="EO8" s="17" t="n"/>
+      <c r="EP8" s="17" t="n"/>
+      <c r="EQ8" s="17" t="n"/>
+      <c r="ER8" s="17" t="n"/>
+      <c r="ES8" s="17" t="n"/>
+      <c r="ET8" s="17" t="n"/>
+      <c r="EU8" s="17" t="n"/>
+      <c r="EV8" s="17" t="n"/>
+      <c r="EW8" s="17" t="n"/>
+      <c r="EX8" s="17" t="n"/>
+      <c r="EY8" s="17" t="n"/>
+      <c r="EZ8" s="17" t="n"/>
+      <c r="FA8" s="17" t="n"/>
+      <c r="FB8" s="17" t="n"/>
+      <c r="FC8" s="17" t="n"/>
+      <c r="FD8" s="19" t="n"/>
+      <c r="FE8" s="19" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="17" t="n">
@@ -750,10 +2136,655 @@
       </c>
       <c r="F9" s="20" t="n"/>
       <c r="G9" s="20" t="n"/>
+      <c r="H9" s="17" t="n"/>
+      <c r="I9" s="17" t="n"/>
+      <c r="J9" s="17" t="n"/>
+      <c r="K9" s="17" t="n"/>
+      <c r="L9" s="17" t="n"/>
+      <c r="M9" s="17" t="n"/>
+      <c r="N9" s="17" t="n"/>
+      <c r="O9" s="17" t="n"/>
+      <c r="P9" s="17" t="n"/>
+      <c r="Q9" s="17" t="n"/>
+      <c r="R9" s="17" t="n"/>
+      <c r="S9" s="17" t="n"/>
+      <c r="T9" s="17" t="n"/>
+      <c r="U9" s="17" t="n"/>
+      <c r="V9" s="17" t="n"/>
+      <c r="W9" s="17" t="n"/>
+      <c r="X9" s="17" t="n"/>
+      <c r="Y9" s="17" t="n"/>
+      <c r="Z9" s="17" t="n"/>
+      <c r="AA9" s="17" t="n"/>
+      <c r="AB9" s="17" t="n"/>
+      <c r="AC9" s="17" t="n"/>
+      <c r="AD9" s="17" t="n"/>
+      <c r="AE9" s="17" t="n"/>
+      <c r="AF9" s="17" t="n"/>
+      <c r="AG9" s="17" t="n"/>
+      <c r="AH9" s="17" t="n"/>
+      <c r="AI9" s="17" t="n"/>
+      <c r="AJ9" s="17" t="n"/>
+      <c r="AK9" s="17" t="n"/>
+      <c r="AL9" s="17" t="n"/>
+      <c r="AM9" s="17" t="n"/>
+      <c r="AN9" s="17" t="n"/>
+      <c r="AO9" s="17" t="n"/>
+      <c r="AP9" s="17" t="n"/>
+      <c r="AQ9" s="17" t="n"/>
+      <c r="AR9" s="17" t="n"/>
+      <c r="AS9" s="17" t="n"/>
+      <c r="AT9" s="17" t="n"/>
+      <c r="AU9" s="17" t="n"/>
+      <c r="AV9" s="17" t="n"/>
+      <c r="AW9" s="17" t="n"/>
+      <c r="AX9" s="17" t="n"/>
+      <c r="AY9" s="17" t="n"/>
+      <c r="AZ9" s="17" t="n"/>
+      <c r="BA9" s="17" t="n"/>
+      <c r="BB9" s="17" t="n"/>
+      <c r="BC9" s="17" t="n"/>
+      <c r="BD9" s="17" t="n"/>
+      <c r="BE9" s="17" t="n"/>
+      <c r="BF9" s="17" t="n"/>
+      <c r="BG9" s="17" t="n"/>
+      <c r="BH9" s="17" t="n"/>
+      <c r="BI9" s="17" t="n"/>
+      <c r="BJ9" s="17" t="n"/>
+      <c r="BK9" s="17" t="n"/>
+      <c r="BL9" s="17" t="n"/>
+      <c r="BM9" s="17" t="n"/>
+      <c r="BN9" s="17" t="n"/>
+      <c r="BO9" s="17" t="n"/>
+      <c r="BP9" s="17" t="n"/>
+      <c r="BQ9" s="17" t="n"/>
+      <c r="BR9" s="17" t="n"/>
+      <c r="BS9" s="17" t="n"/>
+      <c r="BT9" s="17" t="n"/>
+      <c r="BU9" s="17" t="n"/>
+      <c r="BV9" s="17" t="n"/>
+      <c r="BW9" s="17" t="n"/>
+      <c r="BX9" s="17" t="n"/>
+      <c r="BY9" s="17" t="n"/>
+      <c r="BZ9" s="17" t="n"/>
+      <c r="CA9" s="17" t="n"/>
+      <c r="CB9" s="17" t="n"/>
+      <c r="CC9" s="17" t="n"/>
+      <c r="CD9" s="17" t="n"/>
+      <c r="CE9" s="17" t="n"/>
+      <c r="CF9" s="17" t="n"/>
+      <c r="CG9" s="17" t="n"/>
+      <c r="CH9" s="17" t="n"/>
+      <c r="CI9" s="17" t="n"/>
+      <c r="CJ9" s="17" t="n"/>
+      <c r="CK9" s="17" t="n"/>
+      <c r="CL9" s="17" t="n"/>
+      <c r="CM9" s="17" t="n"/>
+      <c r="CN9" s="17" t="n"/>
+      <c r="CO9" s="17" t="n"/>
+      <c r="CP9" s="17" t="n"/>
+      <c r="CQ9" s="17" t="n"/>
+      <c r="CR9" s="17" t="n"/>
+      <c r="CS9" s="17" t="n"/>
+      <c r="CT9" s="17" t="n"/>
+      <c r="CU9" s="17" t="n"/>
+      <c r="CV9" s="17" t="n"/>
+      <c r="CW9" s="17" t="n"/>
+      <c r="CX9" s="17" t="n"/>
+      <c r="CY9" s="17" t="n"/>
+      <c r="CZ9" s="17" t="n"/>
+      <c r="DA9" s="17" t="n"/>
+      <c r="DB9" s="17" t="n"/>
+      <c r="DC9" s="17" t="n"/>
+      <c r="DD9" s="17" t="n"/>
+      <c r="DE9" s="17" t="n"/>
+      <c r="DF9" s="17" t="n"/>
+      <c r="DG9" s="17" t="n"/>
+      <c r="DH9" s="17" t="n"/>
+      <c r="DI9" s="17" t="n"/>
+      <c r="DJ9" s="17" t="n"/>
+      <c r="DK9" s="17" t="n"/>
+      <c r="DL9" s="17" t="n"/>
+      <c r="DM9" s="17" t="n"/>
+      <c r="DN9" s="17" t="n"/>
+      <c r="DO9" s="17" t="n"/>
+      <c r="DP9" s="17" t="n"/>
+      <c r="DQ9" s="17" t="n"/>
+      <c r="DR9" s="17" t="n"/>
+      <c r="DS9" s="17" t="n"/>
+      <c r="DT9" s="17" t="n"/>
+      <c r="DU9" s="17" t="n"/>
+      <c r="DV9" s="17" t="n"/>
+      <c r="DW9" s="17" t="n"/>
+      <c r="DX9" s="17" t="n"/>
+      <c r="DY9" s="17" t="n"/>
+      <c r="DZ9" s="17" t="n"/>
+      <c r="EA9" s="17" t="n"/>
+      <c r="EB9" s="17" t="n"/>
+      <c r="EC9" s="17" t="n"/>
+      <c r="ED9" s="17" t="n"/>
+      <c r="EE9" s="17" t="n"/>
+      <c r="EF9" s="17" t="n"/>
+      <c r="EG9" s="17" t="n"/>
+      <c r="EH9" s="17" t="n"/>
+      <c r="EI9" s="17" t="n"/>
+      <c r="EJ9" s="17" t="n"/>
+      <c r="EK9" s="17" t="n"/>
+      <c r="EL9" s="17" t="n"/>
+      <c r="EM9" s="17" t="n"/>
+      <c r="EN9" s="17" t="n"/>
+      <c r="EO9" s="17" t="n"/>
+      <c r="EP9" s="17" t="n"/>
+      <c r="EQ9" s="17" t="n"/>
+      <c r="ER9" s="17" t="n"/>
+      <c r="ES9" s="17" t="n"/>
+      <c r="ET9" s="17" t="n"/>
+      <c r="EU9" s="17" t="n"/>
+      <c r="EV9" s="17" t="n"/>
+      <c r="EW9" s="17" t="n"/>
+      <c r="EX9" s="17" t="n"/>
+      <c r="EY9" s="17" t="n"/>
+      <c r="EZ9" s="17" t="n"/>
+      <c r="FA9" s="17" t="n"/>
+      <c r="FB9" s="17" t="n"/>
+      <c r="FC9" s="17" t="n"/>
+      <c r="FD9" s="19" t="n"/>
+      <c r="FE9" s="19" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="n"/>
+      <c r="I10" s="17" t="n"/>
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="17" t="n"/>
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="17" t="n"/>
+      <c r="O10" s="17" t="n"/>
+      <c r="P10" s="17" t="n"/>
+      <c r="Q10" s="17" t="n"/>
+      <c r="R10" s="17" t="n"/>
+      <c r="S10" s="17" t="n"/>
+      <c r="T10" s="17" t="n"/>
+      <c r="U10" s="17" t="n"/>
+      <c r="V10" s="17" t="n"/>
+      <c r="W10" s="17" t="n"/>
+      <c r="X10" s="17" t="n"/>
+      <c r="Y10" s="17" t="n"/>
+      <c r="Z10" s="17" t="n"/>
+      <c r="AA10" s="17" t="n"/>
+      <c r="AB10" s="17" t="n"/>
+      <c r="AC10" s="17" t="n"/>
+      <c r="AD10" s="17" t="n"/>
+      <c r="AE10" s="17" t="n"/>
+      <c r="AF10" s="17" t="n"/>
+      <c r="AG10" s="17" t="n"/>
+      <c r="AH10" s="17" t="n"/>
+      <c r="AI10" s="17" t="n"/>
+      <c r="AJ10" s="17" t="n"/>
+      <c r="AK10" s="17" t="n"/>
+      <c r="AL10" s="17" t="n"/>
+      <c r="AM10" s="17" t="n"/>
+      <c r="AN10" s="17" t="n"/>
+      <c r="AO10" s="17" t="n"/>
+      <c r="AP10" s="17" t="n"/>
+      <c r="AQ10" s="17" t="n"/>
+      <c r="AR10" s="17" t="n"/>
+      <c r="AS10" s="17" t="n"/>
+      <c r="AT10" s="17" t="n"/>
+      <c r="AU10" s="17" t="n"/>
+      <c r="AV10" s="17" t="n"/>
+      <c r="AW10" s="17" t="n"/>
+      <c r="AX10" s="17" t="n"/>
+      <c r="AY10" s="17" t="n"/>
+      <c r="AZ10" s="17" t="n"/>
+      <c r="BA10" s="17" t="n"/>
+      <c r="BB10" s="17" t="n"/>
+      <c r="BC10" s="17" t="n"/>
+      <c r="BD10" s="17" t="n"/>
+      <c r="BE10" s="17" t="n"/>
+      <c r="BF10" s="17" t="n"/>
+      <c r="BG10" s="17" t="n"/>
+      <c r="BH10" s="17" t="n"/>
+      <c r="BI10" s="17" t="n"/>
+      <c r="BJ10" s="17" t="n"/>
+      <c r="BK10" s="17" t="n"/>
+      <c r="BL10" s="17" t="n"/>
+      <c r="BM10" s="17" t="n"/>
+      <c r="BN10" s="17" t="n"/>
+      <c r="BO10" s="17" t="n"/>
+      <c r="BP10" s="17" t="n"/>
+      <c r="BQ10" s="17" t="n"/>
+      <c r="BR10" s="17" t="n"/>
+      <c r="BS10" s="17" t="n"/>
+      <c r="BT10" s="17" t="n"/>
+      <c r="BU10" s="17" t="n"/>
+      <c r="BV10" s="17" t="n"/>
+      <c r="BW10" s="17" t="n"/>
+      <c r="BX10" s="17" t="n"/>
+      <c r="BY10" s="17" t="n"/>
+      <c r="BZ10" s="17" t="n"/>
+      <c r="CA10" s="17" t="n"/>
+      <c r="CB10" s="17" t="n"/>
+      <c r="CC10" s="17" t="n"/>
+      <c r="CD10" s="17" t="n"/>
+      <c r="CE10" s="17" t="n"/>
+      <c r="CF10" s="17" t="n"/>
+      <c r="CG10" s="17" t="n"/>
+      <c r="CH10" s="17" t="n"/>
+      <c r="CI10" s="17" t="n"/>
+      <c r="CJ10" s="17" t="n"/>
+      <c r="CK10" s="17" t="n"/>
+      <c r="CL10" s="17" t="n"/>
+      <c r="CM10" s="17" t="n"/>
+      <c r="CN10" s="17" t="n"/>
+      <c r="CO10" s="17" t="n"/>
+      <c r="CP10" s="17" t="n"/>
+      <c r="CQ10" s="17" t="n"/>
+      <c r="CR10" s="17" t="n"/>
+      <c r="CS10" s="17" t="n"/>
+      <c r="CT10" s="17" t="n"/>
+      <c r="CU10" s="17" t="n"/>
+      <c r="CV10" s="17" t="n"/>
+      <c r="CW10" s="17" t="n"/>
+      <c r="CX10" s="17" t="n"/>
+      <c r="CY10" s="17" t="n"/>
+      <c r="CZ10" s="17" t="n"/>
+      <c r="DA10" s="17" t="n"/>
+      <c r="DB10" s="17" t="n"/>
+      <c r="DC10" s="17" t="n"/>
+      <c r="DD10" s="17" t="n"/>
+      <c r="DE10" s="17" t="n"/>
+      <c r="DF10" s="17" t="n"/>
+      <c r="DG10" s="17" t="n"/>
+      <c r="DH10" s="17" t="n"/>
+      <c r="DI10" s="17" t="n"/>
+      <c r="DJ10" s="17" t="n"/>
+      <c r="DK10" s="17" t="n"/>
+      <c r="DL10" s="17" t="n"/>
+      <c r="DM10" s="17" t="n"/>
+      <c r="DN10" s="17" t="n"/>
+      <c r="DO10" s="17" t="n"/>
+      <c r="DP10" s="17" t="n"/>
+      <c r="DQ10" s="17" t="n"/>
+      <c r="DR10" s="17" t="n"/>
+      <c r="DS10" s="17" t="n"/>
+      <c r="DT10" s="17" t="n"/>
+      <c r="DU10" s="17" t="n"/>
+      <c r="DV10" s="17" t="n"/>
+      <c r="DW10" s="17" t="n"/>
+      <c r="DX10" s="17" t="n"/>
+      <c r="DY10" s="17" t="n"/>
+      <c r="DZ10" s="17" t="n"/>
+      <c r="EA10" s="17" t="n"/>
+      <c r="EB10" s="17" t="n"/>
+      <c r="EC10" s="17" t="n"/>
+      <c r="ED10" s="17" t="n"/>
+      <c r="EE10" s="17" t="n"/>
+      <c r="EF10" s="17" t="n"/>
+      <c r="EG10" s="17" t="n"/>
+      <c r="EH10" s="17" t="n"/>
+      <c r="EI10" s="17" t="n"/>
+      <c r="EJ10" s="17" t="n"/>
+      <c r="EK10" s="17" t="n"/>
+      <c r="EL10" s="17" t="n"/>
+      <c r="EM10" s="17" t="n"/>
+      <c r="EN10" s="17" t="n"/>
+      <c r="EO10" s="17" t="n"/>
+      <c r="EP10" s="17" t="n"/>
+      <c r="EQ10" s="17" t="n"/>
+      <c r="ER10" s="17" t="n"/>
+      <c r="ES10" s="17" t="n"/>
+      <c r="ET10" s="17" t="n"/>
+      <c r="EU10" s="17" t="n"/>
+      <c r="EV10" s="17" t="n"/>
+      <c r="EW10" s="17" t="n"/>
+      <c r="EX10" s="17" t="n"/>
+      <c r="EY10" s="17" t="n"/>
+      <c r="EZ10" s="17" t="n"/>
+      <c r="FA10" s="17" t="n"/>
+      <c r="FB10" s="17" t="n"/>
+      <c r="FC10" s="17" t="n"/>
+      <c r="FD10" s="19" t="n"/>
+      <c r="FE10" s="19" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="17" t="n"/>
+      <c r="I11" s="17" t="n"/>
+      <c r="J11" s="17" t="n"/>
+      <c r="K11" s="17" t="n"/>
+      <c r="L11" s="17" t="n"/>
+      <c r="M11" s="17" t="n"/>
+      <c r="N11" s="17" t="n"/>
+      <c r="O11" s="17" t="n"/>
+      <c r="P11" s="17" t="n"/>
+      <c r="Q11" s="17" t="n"/>
+      <c r="R11" s="17" t="n"/>
+      <c r="S11" s="17" t="n"/>
+      <c r="T11" s="17" t="n"/>
+      <c r="U11" s="17" t="n"/>
+      <c r="V11" s="17" t="n"/>
+      <c r="W11" s="17" t="n"/>
+      <c r="X11" s="17" t="n"/>
+      <c r="Y11" s="17" t="n"/>
+      <c r="Z11" s="17" t="n"/>
+      <c r="AA11" s="17" t="n"/>
+      <c r="AB11" s="17" t="n"/>
+      <c r="AC11" s="17" t="n"/>
+      <c r="AD11" s="17" t="n"/>
+      <c r="AE11" s="17" t="n"/>
+      <c r="AF11" s="17" t="n"/>
+      <c r="AG11" s="17" t="n"/>
+      <c r="AH11" s="17" t="n"/>
+      <c r="AI11" s="17" t="n"/>
+      <c r="AJ11" s="17" t="n"/>
+      <c r="AK11" s="17" t="n"/>
+      <c r="AL11" s="17" t="n"/>
+      <c r="AM11" s="17" t="n"/>
+      <c r="AN11" s="17" t="n"/>
+      <c r="AO11" s="17" t="n"/>
+      <c r="AP11" s="17" t="n"/>
+      <c r="AQ11" s="17" t="n"/>
+      <c r="AR11" s="17" t="n"/>
+      <c r="AS11" s="17" t="n"/>
+      <c r="AT11" s="17" t="n"/>
+      <c r="AU11" s="17" t="n"/>
+      <c r="AV11" s="17" t="n"/>
+      <c r="AW11" s="17" t="n"/>
+      <c r="AX11" s="17" t="n"/>
+      <c r="AY11" s="17" t="n"/>
+      <c r="AZ11" s="17" t="n"/>
+      <c r="BA11" s="17" t="n"/>
+      <c r="BB11" s="17" t="n"/>
+      <c r="BC11" s="17" t="n"/>
+      <c r="BD11" s="17" t="n"/>
+      <c r="BE11" s="17" t="n"/>
+      <c r="BF11" s="17" t="n"/>
+      <c r="BG11" s="17" t="n"/>
+      <c r="BH11" s="17" t="n"/>
+      <c r="BI11" s="17" t="n"/>
+      <c r="BJ11" s="17" t="n"/>
+      <c r="BK11" s="17" t="n"/>
+      <c r="BL11" s="17" t="n"/>
+      <c r="BM11" s="17" t="n"/>
+      <c r="BN11" s="17" t="n"/>
+      <c r="BO11" s="17" t="n"/>
+      <c r="BP11" s="17" t="n"/>
+      <c r="BQ11" s="17" t="n"/>
+      <c r="BR11" s="17" t="n"/>
+      <c r="BS11" s="17" t="n"/>
+      <c r="BT11" s="17" t="n"/>
+      <c r="BU11" s="17" t="n"/>
+      <c r="BV11" s="17" t="n"/>
+      <c r="BW11" s="17" t="n"/>
+      <c r="BX11" s="17" t="n"/>
+      <c r="BY11" s="17" t="n"/>
+      <c r="BZ11" s="17" t="n"/>
+      <c r="CA11" s="17" t="n"/>
+      <c r="CB11" s="17" t="n"/>
+      <c r="CC11" s="17" t="n"/>
+      <c r="CD11" s="17" t="n"/>
+      <c r="CE11" s="17" t="n"/>
+      <c r="CF11" s="17" t="n"/>
+      <c r="CG11" s="17" t="n"/>
+      <c r="CH11" s="17" t="n"/>
+      <c r="CI11" s="17" t="n"/>
+      <c r="CJ11" s="17" t="n"/>
+      <c r="CK11" s="17" t="n"/>
+      <c r="CL11" s="17" t="n"/>
+      <c r="CM11" s="17" t="n"/>
+      <c r="CN11" s="17" t="n"/>
+      <c r="CO11" s="17" t="n"/>
+      <c r="CP11" s="17" t="n"/>
+      <c r="CQ11" s="17" t="n"/>
+      <c r="CR11" s="17" t="n"/>
+      <c r="CS11" s="17" t="n"/>
+      <c r="CT11" s="17" t="n"/>
+      <c r="CU11" s="17" t="n"/>
+      <c r="CV11" s="17" t="n"/>
+      <c r="CW11" s="17" t="n"/>
+      <c r="CX11" s="17" t="n"/>
+      <c r="CY11" s="17" t="n"/>
+      <c r="CZ11" s="17" t="n"/>
+      <c r="DA11" s="17" t="n"/>
+      <c r="DB11" s="17" t="n"/>
+      <c r="DC11" s="17" t="n"/>
+      <c r="DD11" s="17" t="n"/>
+      <c r="DE11" s="17" t="n"/>
+      <c r="DF11" s="17" t="n"/>
+      <c r="DG11" s="17" t="n"/>
+      <c r="DH11" s="17" t="n"/>
+      <c r="DI11" s="17" t="n"/>
+      <c r="DJ11" s="17" t="n"/>
+      <c r="DK11" s="17" t="n"/>
+      <c r="DL11" s="17" t="n"/>
+      <c r="DM11" s="17" t="n"/>
+      <c r="DN11" s="17" t="n"/>
+      <c r="DO11" s="17" t="n"/>
+      <c r="DP11" s="17" t="n"/>
+      <c r="DQ11" s="17" t="n"/>
+      <c r="DR11" s="17" t="n"/>
+      <c r="DS11" s="17" t="n"/>
+      <c r="DT11" s="17" t="n"/>
+      <c r="DU11" s="17" t="n"/>
+      <c r="DV11" s="17" t="n"/>
+      <c r="DW11" s="17" t="n"/>
+      <c r="DX11" s="17" t="n"/>
+      <c r="DY11" s="17" t="n"/>
+      <c r="DZ11" s="17" t="n"/>
+      <c r="EA11" s="17" t="n"/>
+      <c r="EB11" s="17" t="n"/>
+      <c r="EC11" s="17" t="n"/>
+      <c r="ED11" s="17" t="n"/>
+      <c r="EE11" s="17" t="n"/>
+      <c r="EF11" s="17" t="n"/>
+      <c r="EG11" s="17" t="n"/>
+      <c r="EH11" s="17" t="n"/>
+      <c r="EI11" s="17" t="n"/>
+      <c r="EJ11" s="17" t="n"/>
+      <c r="EK11" s="17" t="n"/>
+      <c r="EL11" s="17" t="n"/>
+      <c r="EM11" s="17" t="n"/>
+      <c r="EN11" s="17" t="n"/>
+      <c r="EO11" s="17" t="n"/>
+      <c r="EP11" s="17" t="n"/>
+      <c r="EQ11" s="17" t="n"/>
+      <c r="ER11" s="17" t="n"/>
+      <c r="ES11" s="17" t="n"/>
+      <c r="ET11" s="17" t="n"/>
+      <c r="EU11" s="17" t="n"/>
+      <c r="EV11" s="17" t="n"/>
+      <c r="EW11" s="17" t="n"/>
+      <c r="EX11" s="17" t="n"/>
+      <c r="EY11" s="17" t="n"/>
+      <c r="EZ11" s="17" t="n"/>
+      <c r="FA11" s="17" t="n"/>
+      <c r="FB11" s="17" t="n"/>
+      <c r="FC11" s="17" t="n"/>
+      <c r="FD11" s="19" t="n"/>
+      <c r="FE11" s="19" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="17" t="n"/>
+      <c r="H12" s="17" t="n"/>
+      <c r="I12" s="17" t="n"/>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="17" t="n"/>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="17" t="n"/>
+      <c r="O12" s="17" t="n"/>
+      <c r="P12" s="17" t="n"/>
+      <c r="Q12" s="17" t="n"/>
+      <c r="R12" s="17" t="n"/>
+      <c r="S12" s="17" t="n"/>
+      <c r="T12" s="17" t="n"/>
+      <c r="U12" s="17" t="n"/>
+      <c r="V12" s="17" t="n"/>
+      <c r="W12" s="17" t="n"/>
+      <c r="X12" s="17" t="n"/>
+      <c r="Y12" s="17" t="n"/>
+      <c r="Z12" s="17" t="n"/>
+      <c r="AA12" s="17" t="n"/>
+      <c r="AB12" s="17" t="n"/>
+      <c r="AC12" s="17" t="n"/>
+      <c r="AD12" s="17" t="n"/>
+      <c r="AE12" s="17" t="n"/>
+      <c r="AF12" s="17" t="n"/>
+      <c r="AG12" s="17" t="n"/>
+      <c r="AH12" s="17" t="n"/>
+      <c r="AI12" s="17" t="n"/>
+      <c r="AJ12" s="17" t="n"/>
+      <c r="AK12" s="17" t="n"/>
+      <c r="AL12" s="17" t="n"/>
+      <c r="AM12" s="17" t="n"/>
+      <c r="AN12" s="17" t="n"/>
+      <c r="AO12" s="17" t="n"/>
+      <c r="AP12" s="17" t="n"/>
+      <c r="AQ12" s="17" t="n"/>
+      <c r="AR12" s="17" t="n"/>
+      <c r="AS12" s="17" t="n"/>
+      <c r="AT12" s="17" t="n"/>
+      <c r="AU12" s="17" t="n"/>
+      <c r="AV12" s="17" t="n"/>
+      <c r="AW12" s="17" t="n"/>
+      <c r="AX12" s="17" t="n"/>
+      <c r="AY12" s="17" t="n"/>
+      <c r="AZ12" s="17" t="n"/>
+      <c r="BA12" s="17" t="n"/>
+      <c r="BB12" s="17" t="n"/>
+      <c r="BC12" s="17" t="n"/>
+      <c r="BD12" s="17" t="n"/>
+      <c r="BE12" s="17" t="n"/>
+      <c r="BF12" s="17" t="n"/>
+      <c r="BG12" s="17" t="n"/>
+      <c r="BH12" s="17" t="n"/>
+      <c r="BI12" s="17" t="n"/>
+      <c r="BJ12" s="17" t="n"/>
+      <c r="BK12" s="17" t="n"/>
+      <c r="BL12" s="17" t="n"/>
+      <c r="BM12" s="17" t="n"/>
+      <c r="BN12" s="17" t="n"/>
+      <c r="BO12" s="17" t="n"/>
+      <c r="BP12" s="17" t="n"/>
+      <c r="BQ12" s="17" t="n"/>
+      <c r="BR12" s="17" t="n"/>
+      <c r="BS12" s="17" t="n"/>
+      <c r="BT12" s="17" t="n"/>
+      <c r="BU12" s="17" t="n"/>
+      <c r="BV12" s="17" t="n"/>
+      <c r="BW12" s="17" t="n"/>
+      <c r="BX12" s="17" t="n"/>
+      <c r="BY12" s="17" t="n"/>
+      <c r="BZ12" s="17" t="n"/>
+      <c r="CA12" s="17" t="n"/>
+      <c r="CB12" s="17" t="n"/>
+      <c r="CC12" s="17" t="n"/>
+      <c r="CD12" s="17" t="n"/>
+      <c r="CE12" s="17" t="n"/>
+      <c r="CF12" s="17" t="n"/>
+      <c r="CG12" s="17" t="n"/>
+      <c r="CH12" s="17" t="n"/>
+      <c r="CI12" s="17" t="n"/>
+      <c r="CJ12" s="17" t="n"/>
+      <c r="CK12" s="17" t="n"/>
+      <c r="CL12" s="17" t="n"/>
+      <c r="CM12" s="17" t="n"/>
+      <c r="CN12" s="17" t="n"/>
+      <c r="CO12" s="17" t="n"/>
+      <c r="CP12" s="17" t="n"/>
+      <c r="CQ12" s="17" t="n"/>
+      <c r="CR12" s="17" t="n"/>
+      <c r="CS12" s="17" t="n"/>
+      <c r="CT12" s="17" t="n"/>
+      <c r="CU12" s="17" t="n"/>
+      <c r="CV12" s="17" t="n"/>
+      <c r="CW12" s="17" t="n"/>
+      <c r="CX12" s="17" t="n"/>
+      <c r="CY12" s="17" t="n"/>
+      <c r="CZ12" s="17" t="n"/>
+      <c r="DA12" s="17" t="n"/>
+      <c r="DB12" s="17" t="n"/>
+      <c r="DC12" s="17" t="n"/>
+      <c r="DD12" s="17" t="n"/>
+      <c r="DE12" s="17" t="n"/>
+      <c r="DF12" s="17" t="n"/>
+      <c r="DG12" s="17" t="n"/>
+      <c r="DH12" s="17" t="n"/>
+      <c r="DI12" s="17" t="n"/>
+      <c r="DJ12" s="17" t="n"/>
+      <c r="DK12" s="17" t="n"/>
+      <c r="DL12" s="17" t="n"/>
+      <c r="DM12" s="17" t="n"/>
+      <c r="DN12" s="17" t="n"/>
+      <c r="DO12" s="17" t="n"/>
+      <c r="DP12" s="17" t="n"/>
+      <c r="DQ12" s="17" t="n"/>
+      <c r="DR12" s="17" t="n"/>
+      <c r="DS12" s="17" t="n"/>
+      <c r="DT12" s="17" t="n"/>
+      <c r="DU12" s="17" t="n"/>
+      <c r="DV12" s="17" t="n"/>
+      <c r="DW12" s="17" t="n"/>
+      <c r="DX12" s="17" t="n"/>
+      <c r="DY12" s="17" t="n"/>
+      <c r="DZ12" s="17" t="n"/>
+      <c r="EA12" s="17" t="n"/>
+      <c r="EB12" s="17" t="n"/>
+      <c r="EC12" s="17" t="n"/>
+      <c r="ED12" s="17" t="n"/>
+      <c r="EE12" s="17" t="n"/>
+      <c r="EF12" s="17" t="n"/>
+      <c r="EG12" s="17" t="n"/>
+      <c r="EH12" s="17" t="n"/>
+      <c r="EI12" s="17" t="n"/>
+      <c r="EJ12" s="17" t="n"/>
+      <c r="EK12" s="17" t="n"/>
+      <c r="EL12" s="17" t="n"/>
+      <c r="EM12" s="17" t="n"/>
+      <c r="EN12" s="17" t="n"/>
+      <c r="EO12" s="17" t="n"/>
+      <c r="EP12" s="17" t="n"/>
+      <c r="EQ12" s="17" t="n"/>
+      <c r="ER12" s="17" t="n"/>
+      <c r="ES12" s="17" t="n"/>
+      <c r="ET12" s="17" t="n"/>
+      <c r="EU12" s="17" t="n"/>
+      <c r="EV12" s="17" t="n"/>
+      <c r="EW12" s="17" t="n"/>
+      <c r="EX12" s="17" t="n"/>
+      <c r="EY12" s="17" t="n"/>
+      <c r="EZ12" s="17" t="n"/>
+      <c r="FA12" s="17" t="n"/>
+      <c r="FB12" s="17" t="n"/>
+      <c r="FC12" s="17" t="n"/>
+      <c r="FD12" s="20" t="n"/>
+      <c r="FE12" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="FD6:FD12"/>
     <mergeCell ref="F6:F9"/>
+    <mergeCell ref="FE6:FE12"/>
     <mergeCell ref="G6:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2669,13 +4700,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ED4B271-E36E-4423-9AD8-8A7D6411E1A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B89A73A-D035-4FA1-BB34-A6712BFB15A4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEAF7B52-4FEB-4740-BC25-5EF56EDEA0FB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3A1856C-4D59-41DB-88AB-0ED5640BE250}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF92B90-5FA6-4A72-98B0-AE6016D11637}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F3F06EB-F2ED-49C1-A401-653D58073D77}"/>
 </file>
--- a/Pradiniai.xlsx
+++ b/Pradiniai.xlsx
@@ -4700,13 +4700,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B89A73A-D035-4FA1-BB34-A6712BFB15A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54EFCDF5-F7AE-4A25-90A3-7A979126556C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3A1856C-4D59-41DB-88AB-0ED5640BE250}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69660A51-95D6-497F-B030-1F7362E3001F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F3F06EB-F2ED-49C1-A401-653D58073D77}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA75B8D3-5CA5-46FD-8109-2A7CC2F12D01}"/>
 </file>
--- a/Pradiniai.xlsx
+++ b/Pradiniai.xlsx
@@ -4700,13 +4700,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54EFCDF5-F7AE-4A25-90A3-7A979126556C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{488245E5-C5F7-48D7-8D97-67D49CB79722}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69660A51-95D6-497F-B030-1F7362E3001F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{878EBFBD-42B0-4E4B-A664-DB7F8CCA23CF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA75B8D3-5CA5-46FD-8109-2A7CC2F12D01}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{126F4805-CB63-4E20-82CC-DF9EA4BDF153}"/>
 </file>
--- a/Pradiniai.xlsx
+++ b/Pradiniai.xlsx
@@ -140,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -195,9 +195,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -581,12 +578,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A5:C6"/>
+  <dimension ref="A5:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="25" customWidth="1" style="13" min="1" max="1"/>
     <col width="40" customWidth="1" style="13" min="2" max="2"/>
     <col width="60" customWidth="1" style="13" min="3" max="3"/>
+    <col width="20" customWidth="1" style="13" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="5" ht="40" customHeight="1" s="13">
@@ -605,6 +603,11 @@
           <t>Objekto pavadinimas, adresas, taršos šaltinio Nr.</t>
         </is>
       </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Darbuotojo inicialai</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="50" customHeight="1" s="13">
       <c r="A6" s="14" t="n">
@@ -616,6 +619,11 @@
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>S. Č.</t>
         </is>
       </c>
     </row>
@@ -785,27 +793,27 @@
   </cols>
   <sheetData>
     <row r="5" ht="29" customHeight="1" s="13">
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Ėminių ėmimo laikas t, min.</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Paėmimo greitis, l/min</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>Išretėjimas, -hPa</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>Temperatūra prie aspiratoriaus, Vtr oC</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>Vandens kondensato masė m H2O, kg</t>
         </is>
@@ -818,13 +826,13 @@
       <c r="C6" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="22" t="n">
         <v>25.2</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="F6" s="24" t="n">
+      <c r="F6" s="23" t="n">
         <v>0.005</v>
       </c>
     </row>
@@ -893,67 +901,67 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="n">
+      <c r="A3" s="24" t="n">
         <v>10.02</v>
       </c>
-      <c r="B3" s="25" t="n">
+      <c r="B3" s="24" t="n">
         <v>4.1</v>
       </c>
-      <c r="C3" s="26" t="n">
+      <c r="C3" s="25" t="n">
         <v>40.2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="n">
+      <c r="A4" s="24" t="n">
         <v>9.98</v>
       </c>
-      <c r="B4" s="25" t="n">
+      <c r="B4" s="24" t="n">
         <v>3.9</v>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="25" t="n">
         <v>39.8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="n">
+      <c r="A5" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="25" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>1 filtras</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>1 linija</t>
         </is>
       </c>
-      <c r="G8" s="28" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>2 linija</t>
         </is>
       </c>
-      <c r="M8" s="28" t="inlineStr">
+      <c r="M8" s="27" t="inlineStr">
         <is>
           <t>3 linija</t>
         </is>
       </c>
-      <c r="S8" s="28" t="inlineStr">
+      <c r="S8" s="27" t="inlineStr">
         <is>
           <t>4 linija</t>
         </is>
       </c>
-      <c r="Y8" s="28" t="inlineStr">
+      <c r="Y8" s="27" t="inlineStr">
         <is>
           <t>5 linija</t>
         </is>
@@ -1087,10 +1095,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="n">
+      <c r="A10" s="22" t="n">
         <v>111</v>
       </c>
-      <c r="B10" s="23" t="n">
+      <c r="B10" s="22" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="19" t="n">
@@ -1099,13 +1107,13 @@
       <c r="D10" s="19" t="n">
         <v>112</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="22" t="n">
         <v>113</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="22" t="n">
         <v>121</v>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="22">
         <f>B10</f>
         <v/>
       </c>
@@ -1116,13 +1124,13 @@
       <c r="J10" s="19" t="n">
         <v>122</v>
       </c>
-      <c r="K10" s="23" t="n">
+      <c r="K10" s="22" t="n">
         <v>123</v>
       </c>
-      <c r="M10" s="23" t="n">
+      <c r="M10" s="22" t="n">
         <v>131</v>
       </c>
-      <c r="N10" s="23">
+      <c r="N10" s="22">
         <f>B10</f>
         <v/>
       </c>
@@ -1133,13 +1141,13 @@
       <c r="P10" s="19" t="n">
         <v>132</v>
       </c>
-      <c r="Q10" s="23" t="n">
+      <c r="Q10" s="22" t="n">
         <v>133</v>
       </c>
-      <c r="S10" s="23" t="n">
+      <c r="S10" s="22" t="n">
         <v>141</v>
       </c>
-      <c r="T10" s="23">
+      <c r="T10" s="22">
         <f>B10</f>
         <v/>
       </c>
@@ -1150,13 +1158,13 @@
       <c r="V10" s="19" t="n">
         <v>142</v>
       </c>
-      <c r="W10" s="23" t="n">
+      <c r="W10" s="22" t="n">
         <v>143</v>
       </c>
-      <c r="Y10" s="23" t="n">
+      <c r="Y10" s="22" t="n">
         <v>151</v>
       </c>
-      <c r="Z10" s="23">
+      <c r="Z10" s="22">
         <f>B10</f>
         <v/>
       </c>
@@ -1167,15 +1175,15 @@
       <c r="AB10" s="19" t="n">
         <v>152</v>
       </c>
-      <c r="AC10" s="23" t="n">
+      <c r="AC10" s="22" t="n">
         <v>153</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="n">
+      <c r="A11" s="22" t="n">
         <v>111</v>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="22" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="19" t="n">
@@ -1184,13 +1192,13 @@
       <c r="D11" s="19" t="n">
         <v>112</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="22" t="n">
         <v>113</v>
       </c>
-      <c r="G11" s="23" t="n">
+      <c r="G11" s="22" t="n">
         <v>121</v>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="22">
         <f>B11</f>
         <v/>
       </c>
@@ -1201,13 +1209,13 @@
       <c r="J11" s="19" t="n">
         <v>122</v>
       </c>
-      <c r="K11" s="23" t="n">
+      <c r="K11" s="22" t="n">
         <v>123</v>
       </c>
-      <c r="M11" s="23" t="n">
+      <c r="M11" s="22" t="n">
         <v>131</v>
       </c>
-      <c r="N11" s="23">
+      <c r="N11" s="22">
         <f>B11</f>
         <v/>
       </c>
@@ -1218,13 +1226,13 @@
       <c r="P11" s="19" t="n">
         <v>132</v>
       </c>
-      <c r="Q11" s="23" t="n">
+      <c r="Q11" s="22" t="n">
         <v>133</v>
       </c>
-      <c r="S11" s="23" t="n">
+      <c r="S11" s="22" t="n">
         <v>141</v>
       </c>
-      <c r="T11" s="23">
+      <c r="T11" s="22">
         <f>B11</f>
         <v/>
       </c>
@@ -1235,13 +1243,13 @@
       <c r="V11" s="19" t="n">
         <v>142</v>
       </c>
-      <c r="W11" s="23" t="n">
+      <c r="W11" s="22" t="n">
         <v>143</v>
       </c>
-      <c r="Y11" s="23" t="n">
+      <c r="Y11" s="22" t="n">
         <v>151</v>
       </c>
-      <c r="Z11" s="23">
+      <c r="Z11" s="22">
         <f>B11</f>
         <v/>
       </c>
@@ -1252,15 +1260,15 @@
       <c r="AB11" s="19" t="n">
         <v>152</v>
       </c>
-      <c r="AC11" s="23" t="n">
+      <c r="AC11" s="22" t="n">
         <v>153</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="n">
+      <c r="A12" s="22" t="n">
         <v>111</v>
       </c>
-      <c r="B12" s="23" t="n">
+      <c r="B12" s="22" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="19" t="n">
@@ -1269,13 +1277,13 @@
       <c r="D12" s="19" t="n">
         <v>112</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="22" t="n">
         <v>113</v>
       </c>
-      <c r="G12" s="23" t="n">
+      <c r="G12" s="22" t="n">
         <v>121</v>
       </c>
-      <c r="H12" s="23">
+      <c r="H12" s="22">
         <f>B12</f>
         <v/>
       </c>
@@ -1286,13 +1294,13 @@
       <c r="J12" s="19" t="n">
         <v>122</v>
       </c>
-      <c r="K12" s="23" t="n">
+      <c r="K12" s="22" t="n">
         <v>123</v>
       </c>
-      <c r="M12" s="23" t="n">
+      <c r="M12" s="22" t="n">
         <v>131</v>
       </c>
-      <c r="N12" s="23">
+      <c r="N12" s="22">
         <f>B12</f>
         <v/>
       </c>
@@ -1303,13 +1311,13 @@
       <c r="P12" s="19" t="n">
         <v>132</v>
       </c>
-      <c r="Q12" s="23" t="n">
+      <c r="Q12" s="22" t="n">
         <v>133</v>
       </c>
-      <c r="S12" s="23" t="n">
+      <c r="S12" s="22" t="n">
         <v>141</v>
       </c>
-      <c r="T12" s="23">
+      <c r="T12" s="22">
         <f>B12</f>
         <v/>
       </c>
@@ -1320,13 +1328,13 @@
       <c r="V12" s="19" t="n">
         <v>142</v>
       </c>
-      <c r="W12" s="23" t="n">
+      <c r="W12" s="22" t="n">
         <v>143</v>
       </c>
-      <c r="Y12" s="23" t="n">
+      <c r="Y12" s="22" t="n">
         <v>151</v>
       </c>
-      <c r="Z12" s="23">
+      <c r="Z12" s="22">
         <f>B12</f>
         <v/>
       </c>
@@ -1337,15 +1345,15 @@
       <c r="AB12" s="19" t="n">
         <v>152</v>
       </c>
-      <c r="AC12" s="23" t="n">
+      <c r="AC12" s="22" t="n">
         <v>153</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="n">
+      <c r="A13" s="22" t="n">
         <v>111</v>
       </c>
-      <c r="B13" s="23" t="n">
+      <c r="B13" s="22" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="19" t="n">
@@ -1354,13 +1362,13 @@
       <c r="D13" s="19" t="n">
         <v>112</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="22" t="n">
         <v>113</v>
       </c>
-      <c r="G13" s="23" t="n">
+      <c r="G13" s="22" t="n">
         <v>121</v>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="22">
         <f>B13</f>
         <v/>
       </c>
@@ -1371,13 +1379,13 @@
       <c r="J13" s="19" t="n">
         <v>122</v>
       </c>
-      <c r="K13" s="23" t="n">
+      <c r="K13" s="22" t="n">
         <v>123</v>
       </c>
-      <c r="M13" s="23" t="n">
+      <c r="M13" s="22" t="n">
         <v>131</v>
       </c>
-      <c r="N13" s="23">
+      <c r="N13" s="22">
         <f>B13</f>
         <v/>
       </c>
@@ -1388,13 +1396,13 @@
       <c r="P13" s="19" t="n">
         <v>132</v>
       </c>
-      <c r="Q13" s="23" t="n">
+      <c r="Q13" s="22" t="n">
         <v>133</v>
       </c>
-      <c r="S13" s="23" t="n">
+      <c r="S13" s="22" t="n">
         <v>141</v>
       </c>
-      <c r="T13" s="23">
+      <c r="T13" s="22">
         <f>B13</f>
         <v/>
       </c>
@@ -1405,13 +1413,13 @@
       <c r="V13" s="19" t="n">
         <v>142</v>
       </c>
-      <c r="W13" s="23" t="n">
+      <c r="W13" s="22" t="n">
         <v>143</v>
       </c>
-      <c r="Y13" s="23" t="n">
+      <c r="Y13" s="22" t="n">
         <v>151</v>
       </c>
-      <c r="Z13" s="23">
+      <c r="Z13" s="22">
         <f>B13</f>
         <v/>
       </c>
@@ -1422,39 +1430,39 @@
       <c r="AB13" s="19" t="n">
         <v>152</v>
       </c>
-      <c r="AC13" s="23" t="n">
+      <c r="AC13" s="22" t="n">
         <v>153</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>2 filtras</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>1 linija</t>
         </is>
       </c>
-      <c r="G17" s="28" t="inlineStr">
+      <c r="G17" s="27" t="inlineStr">
         <is>
           <t>2 linija</t>
         </is>
       </c>
-      <c r="M17" s="28" t="inlineStr">
+      <c r="M17" s="27" t="inlineStr">
         <is>
           <t>3 linija</t>
         </is>
       </c>
-      <c r="S17" s="28" t="inlineStr">
+      <c r="S17" s="27" t="inlineStr">
         <is>
           <t>4 linija</t>
         </is>
       </c>
-      <c r="Y17" s="28" t="inlineStr">
+      <c r="Y17" s="27" t="inlineStr">
         <is>
           <t>5 linija</t>
         </is>
@@ -1588,10 +1596,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="n">
+      <c r="A19" s="22" t="n">
         <v>211</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B19" s="22">
         <f>B10</f>
         <v/>
       </c>
@@ -1602,13 +1610,13 @@
       <c r="D19" s="19" t="n">
         <v>212</v>
       </c>
-      <c r="E19" s="23" t="n">
+      <c r="E19" s="22" t="n">
         <v>213</v>
       </c>
-      <c r="G19" s="23" t="n">
+      <c r="G19" s="22" t="n">
         <v>221</v>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="22">
         <f>B10</f>
         <v/>
       </c>
@@ -1619,13 +1627,13 @@
       <c r="J19" s="19" t="n">
         <v>222</v>
       </c>
-      <c r="K19" s="23" t="n">
+      <c r="K19" s="22" t="n">
         <v>223</v>
       </c>
-      <c r="M19" s="23" t="n">
+      <c r="M19" s="22" t="n">
         <v>231</v>
       </c>
-      <c r="N19" s="23">
+      <c r="N19" s="22">
         <f>B10</f>
         <v/>
       </c>
@@ -1636,13 +1644,13 @@
       <c r="P19" s="19" t="n">
         <v>232</v>
       </c>
-      <c r="Q19" s="23" t="n">
+      <c r="Q19" s="22" t="n">
         <v>233</v>
       </c>
-      <c r="S19" s="23" t="n">
+      <c r="S19" s="22" t="n">
         <v>241</v>
       </c>
-      <c r="T19" s="23">
+      <c r="T19" s="22">
         <f>B10</f>
         <v/>
       </c>
@@ -1653,13 +1661,13 @@
       <c r="V19" s="19" t="n">
         <v>242</v>
       </c>
-      <c r="W19" s="23" t="n">
+      <c r="W19" s="22" t="n">
         <v>243</v>
       </c>
-      <c r="Y19" s="23" t="n">
+      <c r="Y19" s="22" t="n">
         <v>251</v>
       </c>
-      <c r="Z19" s="23">
+      <c r="Z19" s="22">
         <f>B10</f>
         <v/>
       </c>
@@ -1670,15 +1678,15 @@
       <c r="AB19" s="19" t="n">
         <v>252</v>
       </c>
-      <c r="AC19" s="23" t="n">
+      <c r="AC19" s="22" t="n">
         <v>253</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="n">
+      <c r="A20" s="22" t="n">
         <v>211</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="22">
         <f>B11</f>
         <v/>
       </c>
@@ -1689,13 +1697,13 @@
       <c r="D20" s="19" t="n">
         <v>212</v>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E20" s="22" t="n">
         <v>213</v>
       </c>
-      <c r="G20" s="23" t="n">
+      <c r="G20" s="22" t="n">
         <v>221</v>
       </c>
-      <c r="H20" s="23">
+      <c r="H20" s="22">
         <f>B11</f>
         <v/>
       </c>
@@ -1706,13 +1714,13 @@
       <c r="J20" s="19" t="n">
         <v>222</v>
       </c>
-      <c r="K20" s="23" t="n">
+      <c r="K20" s="22" t="n">
         <v>223</v>
       </c>
-      <c r="M20" s="23" t="n">
+      <c r="M20" s="22" t="n">
         <v>231</v>
       </c>
-      <c r="N20" s="23">
+      <c r="N20" s="22">
         <f>B11</f>
         <v/>
       </c>
@@ -1723,13 +1731,13 @@
       <c r="P20" s="19" t="n">
         <v>232</v>
       </c>
-      <c r="Q20" s="23" t="n">
+      <c r="Q20" s="22" t="n">
         <v>233</v>
       </c>
-      <c r="S20" s="23" t="n">
+      <c r="S20" s="22" t="n">
         <v>241</v>
       </c>
-      <c r="T20" s="23">
+      <c r="T20" s="22">
         <f>B11</f>
         <v/>
       </c>
@@ -1740,13 +1748,13 @@
       <c r="V20" s="19" t="n">
         <v>242</v>
       </c>
-      <c r="W20" s="23" t="n">
+      <c r="W20" s="22" t="n">
         <v>243</v>
       </c>
-      <c r="Y20" s="23" t="n">
+      <c r="Y20" s="22" t="n">
         <v>251</v>
       </c>
-      <c r="Z20" s="23">
+      <c r="Z20" s="22">
         <f>B11</f>
         <v/>
       </c>
@@ -1757,15 +1765,15 @@
       <c r="AB20" s="19" t="n">
         <v>252</v>
       </c>
-      <c r="AC20" s="23" t="n">
+      <c r="AC20" s="22" t="n">
         <v>253</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="n">
+      <c r="A21" s="22" t="n">
         <v>211</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="22">
         <f>B12</f>
         <v/>
       </c>
@@ -1776,13 +1784,13 @@
       <c r="D21" s="19" t="n">
         <v>212</v>
       </c>
-      <c r="E21" s="23" t="n">
+      <c r="E21" s="22" t="n">
         <v>213</v>
       </c>
-      <c r="G21" s="23" t="n">
+      <c r="G21" s="22" t="n">
         <v>221</v>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="22">
         <f>B12</f>
         <v/>
       </c>
@@ -1793,13 +1801,13 @@
       <c r="J21" s="19" t="n">
         <v>222</v>
       </c>
-      <c r="K21" s="23" t="n">
+      <c r="K21" s="22" t="n">
         <v>223</v>
       </c>
-      <c r="M21" s="23" t="n">
+      <c r="M21" s="22" t="n">
         <v>231</v>
       </c>
-      <c r="N21" s="23">
+      <c r="N21" s="22">
         <f>B12</f>
         <v/>
       </c>
@@ -1810,13 +1818,13 @@
       <c r="P21" s="19" t="n">
         <v>232</v>
       </c>
-      <c r="Q21" s="23" t="n">
+      <c r="Q21" s="22" t="n">
         <v>233</v>
       </c>
-      <c r="S21" s="23" t="n">
+      <c r="S21" s="22" t="n">
         <v>241</v>
       </c>
-      <c r="T21" s="23">
+      <c r="T21" s="22">
         <f>B12</f>
         <v/>
       </c>
@@ -1827,13 +1835,13 @@
       <c r="V21" s="19" t="n">
         <v>242</v>
       </c>
-      <c r="W21" s="23" t="n">
+      <c r="W21" s="22" t="n">
         <v>243</v>
       </c>
-      <c r="Y21" s="23" t="n">
+      <c r="Y21" s="22" t="n">
         <v>251</v>
       </c>
-      <c r="Z21" s="23">
+      <c r="Z21" s="22">
         <f>B12</f>
         <v/>
       </c>
@@ -1844,15 +1852,15 @@
       <c r="AB21" s="19" t="n">
         <v>252</v>
       </c>
-      <c r="AC21" s="23" t="n">
+      <c r="AC21" s="22" t="n">
         <v>253</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="23" t="n">
+      <c r="A22" s="22" t="n">
         <v>211</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B22" s="22">
         <f>B13</f>
         <v/>
       </c>
@@ -1863,13 +1871,13 @@
       <c r="D22" s="19" t="n">
         <v>212</v>
       </c>
-      <c r="E22" s="23" t="n">
+      <c r="E22" s="22" t="n">
         <v>213</v>
       </c>
-      <c r="G22" s="23" t="n">
+      <c r="G22" s="22" t="n">
         <v>221</v>
       </c>
-      <c r="H22" s="23">
+      <c r="H22" s="22">
         <f>B13</f>
         <v/>
       </c>
@@ -1880,13 +1888,13 @@
       <c r="J22" s="19" t="n">
         <v>222</v>
       </c>
-      <c r="K22" s="23" t="n">
+      <c r="K22" s="22" t="n">
         <v>223</v>
       </c>
-      <c r="M22" s="23" t="n">
+      <c r="M22" s="22" t="n">
         <v>231</v>
       </c>
-      <c r="N22" s="23">
+      <c r="N22" s="22">
         <f>B13</f>
         <v/>
       </c>
@@ -1897,13 +1905,13 @@
       <c r="P22" s="19" t="n">
         <v>232</v>
       </c>
-      <c r="Q22" s="23" t="n">
+      <c r="Q22" s="22" t="n">
         <v>233</v>
       </c>
-      <c r="S22" s="23" t="n">
+      <c r="S22" s="22" t="n">
         <v>241</v>
       </c>
-      <c r="T22" s="23">
+      <c r="T22" s="22">
         <f>B13</f>
         <v/>
       </c>
@@ -1914,13 +1922,13 @@
       <c r="V22" s="19" t="n">
         <v>242</v>
       </c>
-      <c r="W22" s="23" t="n">
+      <c r="W22" s="22" t="n">
         <v>243</v>
       </c>
-      <c r="Y22" s="23" t="n">
+      <c r="Y22" s="22" t="n">
         <v>251</v>
       </c>
-      <c r="Z22" s="23">
+      <c r="Z22" s="22">
         <f>B13</f>
         <v/>
       </c>
@@ -1931,39 +1939,39 @@
       <c r="AB22" s="19" t="n">
         <v>252</v>
       </c>
-      <c r="AC22" s="23" t="n">
+      <c r="AC22" s="22" t="n">
         <v>253</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t>3 filtras</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="28" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>1 linija</t>
         </is>
       </c>
-      <c r="G26" s="28" t="inlineStr">
+      <c r="G26" s="27" t="inlineStr">
         <is>
           <t>2 linija</t>
         </is>
       </c>
-      <c r="M26" s="28" t="inlineStr">
+      <c r="M26" s="27" t="inlineStr">
         <is>
           <t>3 linija</t>
         </is>
       </c>
-      <c r="S26" s="28" t="inlineStr">
+      <c r="S26" s="27" t="inlineStr">
         <is>
           <t>4 linija</t>
         </is>
       </c>
-      <c r="Y26" s="28" t="inlineStr">
+      <c r="Y26" s="27" t="inlineStr">
         <is>
           <t>5 linija</t>
         </is>
@@ -2097,10 +2105,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="n">
+      <c r="A28" s="22" t="n">
         <v>311</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B28" s="22">
         <f>B10</f>
         <v/>
       </c>
@@ -2111,13 +2119,13 @@
       <c r="D28" s="19" t="n">
         <v>312</v>
       </c>
-      <c r="E28" s="23" t="n">
+      <c r="E28" s="22" t="n">
         <v>313</v>
       </c>
-      <c r="G28" s="23" t="n">
+      <c r="G28" s="22" t="n">
         <v>321</v>
       </c>
-      <c r="H28" s="23">
+      <c r="H28" s="22">
         <f>B10</f>
         <v/>
       </c>
@@ -2128,13 +2136,13 @@
       <c r="J28" s="19" t="n">
         <v>322</v>
       </c>
-      <c r="K28" s="23" t="n">
+      <c r="K28" s="22" t="n">
         <v>323</v>
       </c>
-      <c r="M28" s="23" t="n">
+      <c r="M28" s="22" t="n">
         <v>331</v>
       </c>
-      <c r="N28" s="23">
+      <c r="N28" s="22">
         <f>B10</f>
         <v/>
       </c>
@@ -2145,13 +2153,13 @@
       <c r="P28" s="19" t="n">
         <v>332</v>
       </c>
-      <c r="Q28" s="23" t="n">
+      <c r="Q28" s="22" t="n">
         <v>333</v>
       </c>
-      <c r="S28" s="23" t="n">
+      <c r="S28" s="22" t="n">
         <v>341</v>
       </c>
-      <c r="T28" s="23">
+      <c r="T28" s="22">
         <f>B10</f>
         <v/>
       </c>
@@ -2162,13 +2170,13 @@
       <c r="V28" s="19" t="n">
         <v>342</v>
       </c>
-      <c r="W28" s="23" t="n">
+      <c r="W28" s="22" t="n">
         <v>343</v>
       </c>
-      <c r="Y28" s="23" t="n">
+      <c r="Y28" s="22" t="n">
         <v>351</v>
       </c>
-      <c r="Z28" s="23">
+      <c r="Z28" s="22">
         <f>B10</f>
         <v/>
       </c>
@@ -2179,15 +2187,15 @@
       <c r="AB28" s="19" t="n">
         <v>352</v>
       </c>
-      <c r="AC28" s="23" t="n">
+      <c r="AC28" s="22" t="n">
         <v>353</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="n">
+      <c r="A29" s="22" t="n">
         <v>311</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B29" s="22">
         <f>B11</f>
         <v/>
       </c>
@@ -2198,13 +2206,13 @@
       <c r="D29" s="19" t="n">
         <v>312</v>
       </c>
-      <c r="E29" s="23" t="n">
+      <c r="E29" s="22" t="n">
         <v>313</v>
       </c>
-      <c r="G29" s="23" t="n">
+      <c r="G29" s="22" t="n">
         <v>321</v>
       </c>
-      <c r="H29" s="23">
+      <c r="H29" s="22">
         <f>B11</f>
         <v/>
       </c>
@@ -2215,13 +2223,13 @@
       <c r="J29" s="19" t="n">
         <v>322</v>
       </c>
-      <c r="K29" s="23" t="n">
+      <c r="K29" s="22" t="n">
         <v>323</v>
       </c>
-      <c r="M29" s="23" t="n">
+      <c r="M29" s="22" t="n">
         <v>331</v>
       </c>
-      <c r="N29" s="23">
+      <c r="N29" s="22">
         <f>B11</f>
         <v/>
       </c>
@@ -2232,13 +2240,13 @@
       <c r="P29" s="19" t="n">
         <v>332</v>
       </c>
-      <c r="Q29" s="23" t="n">
+      <c r="Q29" s="22" t="n">
         <v>333</v>
       </c>
-      <c r="S29" s="23" t="n">
+      <c r="S29" s="22" t="n">
         <v>341</v>
       </c>
-      <c r="T29" s="23">
+      <c r="T29" s="22">
         <f>B11</f>
         <v/>
       </c>
@@ -2249,13 +2257,13 @@
       <c r="V29" s="19" t="n">
         <v>342</v>
       </c>
-      <c r="W29" s="23" t="n">
+      <c r="W29" s="22" t="n">
         <v>343</v>
       </c>
-      <c r="Y29" s="23" t="n">
+      <c r="Y29" s="22" t="n">
         <v>351</v>
       </c>
-      <c r="Z29" s="23">
+      <c r="Z29" s="22">
         <f>B11</f>
         <v/>
       </c>
@@ -2266,15 +2274,15 @@
       <c r="AB29" s="19" t="n">
         <v>352</v>
       </c>
-      <c r="AC29" s="23" t="n">
+      <c r="AC29" s="22" t="n">
         <v>353</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="23" t="n">
+      <c r="A30" s="22" t="n">
         <v>311</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B30" s="22">
         <f>B12</f>
         <v/>
       </c>
@@ -2285,13 +2293,13 @@
       <c r="D30" s="19" t="n">
         <v>312</v>
       </c>
-      <c r="E30" s="23" t="n">
+      <c r="E30" s="22" t="n">
         <v>313</v>
       </c>
-      <c r="G30" s="23" t="n">
+      <c r="G30" s="22" t="n">
         <v>321</v>
       </c>
-      <c r="H30" s="23">
+      <c r="H30" s="22">
         <f>B12</f>
         <v/>
       </c>
@@ -2302,13 +2310,13 @@
       <c r="J30" s="19" t="n">
         <v>322</v>
       </c>
-      <c r="K30" s="23" t="n">
+      <c r="K30" s="22" t="n">
         <v>323</v>
       </c>
-      <c r="M30" s="23" t="n">
+      <c r="M30" s="22" t="n">
         <v>331</v>
       </c>
-      <c r="N30" s="23">
+      <c r="N30" s="22">
         <f>B12</f>
         <v/>
       </c>
@@ -2319,13 +2327,13 @@
       <c r="P30" s="19" t="n">
         <v>332</v>
       </c>
-      <c r="Q30" s="23" t="n">
+      <c r="Q30" s="22" t="n">
         <v>333</v>
       </c>
-      <c r="S30" s="23" t="n">
+      <c r="S30" s="22" t="n">
         <v>341</v>
       </c>
-      <c r="T30" s="23">
+      <c r="T30" s="22">
         <f>B12</f>
         <v/>
       </c>
@@ -2336,13 +2344,13 @@
       <c r="V30" s="19" t="n">
         <v>342</v>
       </c>
-      <c r="W30" s="23" t="n">
+      <c r="W30" s="22" t="n">
         <v>343</v>
       </c>
-      <c r="Y30" s="23" t="n">
+      <c r="Y30" s="22" t="n">
         <v>351</v>
       </c>
-      <c r="Z30" s="23">
+      <c r="Z30" s="22">
         <f>B12</f>
         <v/>
       </c>
@@ -2353,15 +2361,15 @@
       <c r="AB30" s="19" t="n">
         <v>352</v>
       </c>
-      <c r="AC30" s="23" t="n">
+      <c r="AC30" s="22" t="n">
         <v>353</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="n">
+      <c r="A31" s="22" t="n">
         <v>311</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B31" s="22">
         <f>B13</f>
         <v/>
       </c>
@@ -2372,13 +2380,13 @@
       <c r="D31" s="19" t="n">
         <v>312</v>
       </c>
-      <c r="E31" s="23" t="n">
+      <c r="E31" s="22" t="n">
         <v>313</v>
       </c>
-      <c r="G31" s="23" t="n">
+      <c r="G31" s="22" t="n">
         <v>321</v>
       </c>
-      <c r="H31" s="23">
+      <c r="H31" s="22">
         <f>B13</f>
         <v/>
       </c>
@@ -2389,13 +2397,13 @@
       <c r="J31" s="19" t="n">
         <v>322</v>
       </c>
-      <c r="K31" s="23" t="n">
+      <c r="K31" s="22" t="n">
         <v>323</v>
       </c>
-      <c r="M31" s="23" t="n">
+      <c r="M31" s="22" t="n">
         <v>331</v>
       </c>
-      <c r="N31" s="23">
+      <c r="N31" s="22">
         <f>B13</f>
         <v/>
       </c>
@@ -2406,13 +2414,13 @@
       <c r="P31" s="19" t="n">
         <v>332</v>
       </c>
-      <c r="Q31" s="23" t="n">
+      <c r="Q31" s="22" t="n">
         <v>333</v>
       </c>
-      <c r="S31" s="23" t="n">
+      <c r="S31" s="22" t="n">
         <v>341</v>
       </c>
-      <c r="T31" s="23">
+      <c r="T31" s="22">
         <f>B13</f>
         <v/>
       </c>
@@ -2423,13 +2431,13 @@
       <c r="V31" s="19" t="n">
         <v>342</v>
       </c>
-      <c r="W31" s="23" t="n">
+      <c r="W31" s="22" t="n">
         <v>343</v>
       </c>
-      <c r="Y31" s="23" t="n">
+      <c r="Y31" s="22" t="n">
         <v>351</v>
       </c>
-      <c r="Z31" s="23">
+      <c r="Z31" s="22">
         <f>B13</f>
         <v/>
       </c>
@@ -2440,7 +2448,7 @@
       <c r="AB31" s="19" t="n">
         <v>352</v>
       </c>
-      <c r="AC31" s="23" t="n">
+      <c r="AC31" s="22" t="n">
         <v>353</v>
       </c>
     </row>
@@ -2464,291 +2472,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumentas" ma:contentTypeID="0x010100BAB57CF81AE55C4698AAD22D302297F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Kurkite naują dokumentą." ma:contentTypeScope="" ma:versionID="49ab401eb4052690d2a2629974c22fd6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="453e7e53-5eb2-45cf-b2ab-34c867e554b8" xmlns:ns3="aa0d983d-359a-438c-9953-3af1a8ac0831" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab9969d50e0b13c63bc5bd0499c928dc" ns2:_="" ns3:_="">
-    <xsd:import namespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
-    <xsd:import namespace="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="15" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="16" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Vaizdų žymės" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="993cf2ba-b7a7-49f7-97d1-76e12a88c412" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="23" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="aa0d983d-359a-438c-9953-3af1a8ac0831" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{82c4fa3c-500e-4213-91e5-1b9e2014ea63}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="aa0d983d-359a-438c-9953-3af1a8ac0831">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="21" nillable="true" ma:displayName="Bendrinama su" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="22" nillable="true" ma:displayName="Bendrinta su išsamia informacija" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Turinio tipas"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Antraštė"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="453e7e53-5eb2-45cf-b2ab-34c867e554b8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="aa0d983d-359a-438c-9953-3af1a8ac0831" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{914E1BA1-4396-4E1F-B46F-813BDD05E393}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB985D69-6046-40A7-A96E-D0B4F599B01D}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE3D0EA8-2B82-4F18-85D5-5650815FB10C}"/>
 </file>
--- a/Pradiniai.xlsx
+++ b/Pradiniai.xlsx
@@ -22,13 +22,18 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -47,12 +52,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -134,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -142,53 +162,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -559,13 +582,13 @@
   <dimension ref="A5:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="25" customWidth="1" style="13" min="1" max="1"/>
-    <col width="40" customWidth="1" style="13" min="2" max="2"/>
-    <col width="60" customWidth="1" style="13" min="3" max="3"/>
-    <col width="20" customWidth="1" style="13" min="4" max="4"/>
+    <col width="25" customWidth="1" style="11" min="1" max="1"/>
+    <col width="40" customWidth="1" style="11" min="2" max="2"/>
+    <col width="60" customWidth="1" style="11" min="3" max="3"/>
+    <col width="20" customWidth="1" style="11" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="5" ht="40" customHeight="1" s="13">
+    <row r="5" ht="40" customHeight="1" s="11">
       <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Matavimo data</t>
@@ -587,8 +610,8 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="50" customHeight="1" s="13">
-      <c r="A6" s="14" t="n">
+    <row r="6" ht="50" customHeight="1" s="11">
+      <c r="A6" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="B6" s="2" t="n">
@@ -619,107 +642,107 @@
   <dimension ref="A5:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="15" customWidth="1" style="13" min="1" max="2"/>
-    <col width="15" customWidth="1" style="13" min="2" max="2"/>
-    <col width="18" customWidth="1" style="13" min="3" max="4"/>
-    <col width="18" customWidth="1" style="13" min="4" max="4"/>
+    <col width="15" customWidth="1" style="11" min="1" max="2"/>
+    <col width="15" customWidth="1" style="11" min="2" max="2"/>
+    <col width="18" customWidth="1" style="11" min="3" max="4"/>
+    <col width="18" customWidth="1" style="11" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="5" ht="58" customHeight="1" s="13">
-      <c r="A5" s="15" t="inlineStr">
+    <row r="5" ht="58" customHeight="1" s="11">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Išmatuotas diferencinis slėgis taškuose 1 linija, Pdi, hPa</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Išmatuotas diferencinis slėgis taškuose 2 linija, Pdi, hPa</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Atmosferinis slėgis P, hPa</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="17" t="n">
         <v>0.73</v>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>0.61</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>1012</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>0.35</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="17" t="n">
         <v>0.87</v>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>0.76</v>
       </c>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="17" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>0.78</v>
       </c>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="18" t="n"/>
+      <c r="C8" s="19" t="n"/>
+      <c r="D8" s="19" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n">
+      <c r="A9" s="17" t="n">
         <v>0.92</v>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>0.87</v>
       </c>
-      <c r="C9" s="18" t="n"/>
-      <c r="D9" s="18" t="n"/>
+      <c r="C9" s="19" t="n"/>
+      <c r="D9" s="19" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n">
+      <c r="A10" s="17" t="n">
         <v>0.86</v>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>0.82</v>
       </c>
-      <c r="C10" s="18" t="n"/>
-      <c r="D10" s="18" t="n"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="19" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n">
+      <c r="A11" s="17" t="n">
         <v>0.77</v>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="C11" s="18" t="n"/>
-      <c r="D11" s="18" t="n"/>
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="19" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n">
+      <c r="A12" s="17" t="n">
         <v>0.7</v>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>0.75</v>
       </c>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -739,54 +762,54 @@
   <dimension ref="B5:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="22" customWidth="1" style="13" min="2" max="6"/>
-    <col width="22" customWidth="1" style="13" min="3" max="3"/>
-    <col width="22" customWidth="1" style="13" min="4" max="4"/>
-    <col width="22" customWidth="1" style="13" min="5" max="5"/>
-    <col width="22" customWidth="1" style="13" min="6" max="6"/>
+    <col width="22" customWidth="1" style="11" min="2" max="6"/>
+    <col width="22" customWidth="1" style="11" min="3" max="3"/>
+    <col width="22" customWidth="1" style="11" min="4" max="4"/>
+    <col width="22" customWidth="1" style="11" min="5" max="5"/>
+    <col width="22" customWidth="1" style="11" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="5" ht="29" customHeight="1" s="13">
-      <c r="B5" s="15" t="inlineStr">
+    <row r="5" ht="29" customHeight="1" s="11">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Ėminių ėmimo laikas t, min.</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Paėmimo greitis, l/min</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>Išretėjimas, -hPa</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>Temperatūra prie aspiratoriaus, Vtr oC</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>Vandens kondensato masė m H2O, kg</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="21" t="n">
         <v>27.2</v>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="21" t="n">
         <v>12.7</v>
       </c>
-      <c r="F6" s="21" t="n">
+      <c r="F6" s="22" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -804,377 +827,377 @@
   <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="18" customWidth="1" style="13" min="1" max="12"/>
-    <col width="18" customWidth="1" style="13" min="2" max="2"/>
-    <col width="18" customWidth="1" style="13" min="3" max="3"/>
-    <col width="18" customWidth="1" style="13" min="4" max="4"/>
-    <col width="18" customWidth="1" style="13" min="5" max="5"/>
-    <col width="18" customWidth="1" style="13" min="6" max="6"/>
-    <col width="18" customWidth="1" style="13" min="7" max="7"/>
-    <col width="18" customWidth="1" style="13" min="8" max="8"/>
-    <col width="18" customWidth="1" style="13" min="9" max="9"/>
-    <col width="18" customWidth="1" style="13" min="10" max="10"/>
-    <col width="18" customWidth="1" style="13" min="11" max="11"/>
-    <col width="18" customWidth="1" style="13" min="12" max="12"/>
+    <col width="18" customWidth="1" style="11" min="1" max="12"/>
+    <col width="18" customWidth="1" style="11" min="2" max="2"/>
+    <col width="18" customWidth="1" style="11" min="3" max="3"/>
+    <col width="18" customWidth="1" style="11" min="4" max="4"/>
+    <col width="18" customWidth="1" style="11" min="5" max="5"/>
+    <col width="18" customWidth="1" style="11" min="6" max="6"/>
+    <col width="18" customWidth="1" style="11" min="7" max="7"/>
+    <col width="18" customWidth="1" style="11" min="8" max="8"/>
+    <col width="18" customWidth="1" style="11" min="9" max="9"/>
+    <col width="18" customWidth="1" style="11" min="10" max="10"/>
+    <col width="18" customWidth="1" style="11" min="11" max="11"/>
+    <col width="18" customWidth="1" style="11" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2" ht="29" customHeight="1" s="13">
-      <c r="A2" s="15" t="inlineStr">
+    <row r="2" ht="29" customHeight="1" s="11">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Išmatuota O2 koncentracija (%)</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Išmatuota CO2 koncentracija (%)</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>Temperatūra ortakyje tor (°C)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="17" t="n">
         <v>7.92</v>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>7.41</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="C3" s="21" t="n">
         <v>63.1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="17" t="n">
         <v>7.94</v>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>7.4</v>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="21" t="n">
         <v>62.7</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="17" t="n">
         <v>7.96</v>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>7.39</v>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="21" t="n">
         <v>63.3</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>1 filtras</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>1 linija</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>2 linija</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="43.5" customHeight="1" s="13">
-      <c r="A9" s="15" t="inlineStr">
+    <row r="9" ht="43.5" customHeight="1" s="11">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Slėgis prieš rotametrą ΔPr (±hPa)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Antgalio diametras da (mm)</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Siurbimo laikas t (min)</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>Siurbimo greitis Vo (l/min)</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>Siurbiamų dujų temperatūra prieš rotametrą tr (°C)</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>Slėgis prieš rotametrą ΔPr (±hPa)</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t>Antgalio diametras da (mm)</t>
         </is>
       </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>Siurbimo laikas t (min)</t>
         </is>
       </c>
-      <c r="J9" s="15" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t>Siurbimo greitis Vo (l/min)</t>
         </is>
       </c>
-      <c r="K9" s="15" t="inlineStr">
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t>Siurbiamų dujų temperatūra prieš rotametrą tr (°C)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="21" t="n">
         <v>58.6</v>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G10" s="21" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="H10" s="21">
+        <f>B10</f>
+        <v/>
+      </c>
+      <c r="I10" s="18">
+        <f>C10</f>
+        <v/>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="B11" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="H11" s="21">
+        <f>B11</f>
+        <v/>
+      </c>
+      <c r="I11" s="18">
+        <f>C11</f>
+        <v/>
+      </c>
+      <c r="J11" s="18" t="n">
         <v>11</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="K11" s="21" t="n">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="B12" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="H12" s="21">
+        <f>B12</f>
+        <v/>
+      </c>
+      <c r="I12" s="18">
+        <f>C12</f>
+        <v/>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="B13" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="H13" s="21">
+        <f>B13</f>
+        <v/>
+      </c>
+      <c r="I13" s="18">
+        <f>C13</f>
+        <v/>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="K13" s="21" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="B14" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="H14" s="21">
+        <f>B14</f>
+        <v/>
+      </c>
+      <c r="I14" s="18">
+        <f>C14</f>
+        <v/>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="K14" s="21" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="B15" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="H15" s="21">
+        <f>B15</f>
+        <v/>
+      </c>
+      <c r="I15" s="18">
+        <f>C15</f>
+        <v/>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="K15" s="21" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="B16" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="E16" s="21" t="n">
         <v>13.4</v>
       </c>
-      <c r="G10" s="20" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="H10" s="20">
-        <f>B10</f>
-        <v/>
-      </c>
-      <c r="I10" s="17">
-        <f>C10</f>
-        <v/>
-      </c>
-      <c r="J10" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="K10" s="20" t="n">
-        <v>13.7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="B11" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="E11" s="20" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="G11" s="20" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="H11" s="20">
-        <f>B11</f>
-        <v/>
-      </c>
-      <c r="I11" s="17">
-        <f>C11</f>
-        <v/>
-      </c>
-      <c r="J11" s="17" t="n">
+      <c r="G16" s="21" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="H16" s="21">
+        <f>B16</f>
+        <v/>
+      </c>
+      <c r="I16" s="18">
+        <f>C16</f>
+        <v/>
+      </c>
+      <c r="J16" s="18" t="n">
         <v>11</v>
       </c>
-      <c r="K11" s="20" t="n">
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="B12" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="G12" s="20" t="n">
-        <v>67.90000000000001</v>
-      </c>
-      <c r="H12" s="20">
-        <f>B12</f>
-        <v/>
-      </c>
-      <c r="I12" s="17">
-        <f>C12</f>
-        <v/>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="B13" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="E13" s="20" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="G13" s="20" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="H13" s="20">
-        <f>B13</f>
-        <v/>
-      </c>
-      <c r="I13" s="17">
-        <f>C13</f>
-        <v/>
-      </c>
-      <c r="J13" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>13.7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="B14" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="E14" s="20" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="G14" s="20" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="H14" s="20">
-        <f>B14</f>
-        <v/>
-      </c>
-      <c r="I14" s="17">
-        <f>C14</f>
-        <v/>
-      </c>
-      <c r="J14" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="K14" s="20" t="n">
-        <v>13.7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="B15" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="E15" s="20" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="G15" s="20" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="H15" s="20">
-        <f>B15</f>
-        <v/>
-      </c>
-      <c r="I15" s="17">
-        <f>C15</f>
-        <v/>
-      </c>
-      <c r="J15" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="K15" s="20" t="n">
-        <v>13.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="B16" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" s="20" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="G16" s="20" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="H16" s="20">
-        <f>B16</f>
-        <v/>
-      </c>
-      <c r="I16" s="17">
-        <f>C16</f>
-        <v/>
-      </c>
-      <c r="J16" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="K16" s="20" t="n">
+      <c r="K16" s="21" t="n">
         <v>13.7</v>
       </c>
     </row>
